--- a/backup/Human And AI.xlsx
+++ b/backup/Human And AI.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PENDIDIKAN S2\S4\SENTIMEN ABSA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\sentimen-absa\backup\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF3C5EAA-B3CB-4CEE-AA1C-D5C0E6A27982}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7FF574-3A01-45B2-9847-6585B4CA7FDD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{EEFE1E53-11F5-483E-9F4B-F5340641D176}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{EEFE1E53-11F5-483E-9F4B-F5340641D176}"/>
   </bookViews>
   <sheets>
     <sheet name="TABEL ASPEK" sheetId="4" r:id="rId1"/>
@@ -9203,11 +9203,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDEAA580-5D1C-40EE-AC9D-F924AE642C13}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -9217,8 +9217,8 @@
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
     </row>
-    <row r="2" spans="1:3" ht="15" thickBot="1"/>
-    <row r="3" spans="1:3" ht="15.5" thickBot="1">
+    <row r="2" spans="1:3" ht="15.75" thickBot="1"/>
+    <row r="3" spans="1:3" ht="16.5" thickBot="1">
       <c r="A3" s="17" t="s">
         <v>2789</v>
       </c>
@@ -9229,7 +9229,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="31.5" thickBot="1">
+    <row r="4" spans="1:3" ht="32.25" thickBot="1">
       <c r="A4" s="19">
         <v>1</v>
       </c>
@@ -9240,7 +9240,7 @@
         <v>2792</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="31.5" thickBot="1">
+    <row r="5" spans="1:3" ht="32.25" thickBot="1">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -9251,7 +9251,7 @@
         <v>2793</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="31.5" thickBot="1">
+    <row r="6" spans="1:3" ht="32.25" thickBot="1">
       <c r="A6" s="19">
         <v>3</v>
       </c>
@@ -9262,7 +9262,7 @@
         <v>2794</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="47" thickBot="1">
+    <row r="7" spans="1:3" ht="48" thickBot="1">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -9273,7 +9273,7 @@
         <v>2795</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="31.5" thickBot="1">
+    <row r="8" spans="1:3" ht="32.25" thickBot="1">
       <c r="A8" s="19">
         <v>5</v>
       </c>
@@ -9284,7 +9284,7 @@
         <v>2796</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="47" thickBot="1">
+    <row r="9" spans="1:3" ht="48" thickBot="1">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="47" thickBot="1">
+    <row r="10" spans="1:3" ht="48" thickBot="1">
       <c r="A10" s="19">
         <v>7</v>
       </c>
@@ -9306,7 +9306,7 @@
         <v>2798</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="47" thickBot="1">
+    <row r="11" spans="1:3" ht="48" thickBot="1">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>2799</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="31.5" thickBot="1">
+    <row r="12" spans="1:3" ht="32.25" thickBot="1">
       <c r="A12" s="19">
         <v>9</v>
       </c>
@@ -9340,19 +9340,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F2C7157-3EED-4A14-9A59-C1747CACA7A9}">
   <dimension ref="A1:M810"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="102.7265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="17.81640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="72.54296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="102.7109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.5703125" style="2" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.453125" customWidth="1"/>
-    <col min="8" max="8" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9420,7 +9420,7 @@
         <v>2786</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="29">
+    <row r="3" spans="1:13" ht="30">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -9461,7 +9461,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="29">
+    <row r="4" spans="1:13" ht="30">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -9502,7 +9502,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="29">
+    <row r="5" spans="1:13" ht="30">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -9543,7 +9543,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="43.5">
+    <row r="6" spans="1:13" ht="45">
       <c r="A6" s="1">
         <v>4</v>
       </c>
@@ -9625,7 +9625,7 @@
         <v>0.73170000000000002</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="43.5">
+    <row r="8" spans="1:13" ht="45">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -9666,7 +9666,7 @@
         <v>0.70369999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="43.5">
+    <row r="9" spans="1:13" ht="45">
       <c r="A9" s="1">
         <v>7</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="43.5">
+    <row r="10" spans="1:13" ht="45">
       <c r="A10" s="1">
         <v>8</v>
       </c>
@@ -9789,7 +9789,7 @@
         <v>0.73170000000000002</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="43.5">
+    <row r="12" spans="1:13" ht="45">
       <c r="A12" s="1">
         <v>10</v>
       </c>
@@ -9830,7 +9830,7 @@
         <v>0.8085</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="29">
+    <row r="13" spans="1:13" ht="30">
       <c r="A13" s="1">
         <v>11</v>
       </c>
@@ -9871,7 +9871,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="29">
+    <row r="14" spans="1:13" ht="30">
       <c r="A14" s="1">
         <v>12</v>
       </c>
@@ -9912,7 +9912,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="29">
+    <row r="15" spans="1:13" ht="30">
       <c r="A15" s="1">
         <v>13</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="29">
+    <row r="16" spans="1:13" ht="30">
       <c r="A16" s="1">
         <v>14</v>
       </c>
@@ -9994,7 +9994,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="29">
+    <row r="17" spans="1:13" ht="45">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -10035,7 +10035,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="29">
+    <row r="18" spans="1:13" ht="30">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="29">
+    <row r="19" spans="1:13" ht="30">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -10117,7 +10117,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="29">
+    <row r="20" spans="1:13" ht="30">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -10158,7 +10158,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="29">
+    <row r="21" spans="1:13" ht="30">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>0.8276</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="29">
+    <row r="22" spans="1:13" ht="30">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>0.78569999999999995</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="29">
+    <row r="23" spans="1:13" ht="30">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -10281,7 +10281,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="29">
+    <row r="24" spans="1:13" ht="30">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="43.5">
+    <row r="25" spans="1:13" ht="45">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="29">
+    <row r="26" spans="1:13" ht="30">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>0.89470000000000005</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="43.5">
+    <row r="27" spans="1:13" ht="45">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -10445,7 +10445,7 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="43.5">
+    <row r="28" spans="1:13" ht="45">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -10486,7 +10486,7 @@
         <v>0.52459999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="29">
+    <row r="29" spans="1:13" ht="30">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="43.5">
+    <row r="30" spans="1:13" ht="45">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -10568,7 +10568,7 @@
         <v>0.6512</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="29">
+    <row r="31" spans="1:13" ht="30">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -10609,7 +10609,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="29">
+    <row r="32" spans="1:13" ht="30">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -10650,7 +10650,7 @@
         <v>0.38100000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="29">
+    <row r="33" spans="1:13" ht="45">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -10691,7 +10691,7 @@
         <v>0.6341</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="29">
+    <row r="34" spans="1:13" ht="30">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -10732,7 +10732,7 @@
         <v>0.68420000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="29">
+    <row r="35" spans="1:13" ht="30">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>0.1212</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="29">
+    <row r="36" spans="1:13" ht="30">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -10814,7 +10814,7 @@
         <v>0.54049999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:13" ht="30">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -10855,7 +10855,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="29">
+    <row r="38" spans="1:13" ht="30">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -10933,7 +10933,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="29">
+    <row r="40" spans="1:13" ht="30">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -10974,7 +10974,7 @@
         <v>0.3226</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="29">
+    <row r="41" spans="1:13" ht="30">
       <c r="A41" s="1">
         <v>39</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="29">
+    <row r="42" spans="1:13" ht="30">
       <c r="A42" s="1">
         <v>40</v>
       </c>
@@ -11056,7 +11056,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="43.5">
+    <row r="43" spans="1:13" ht="45">
       <c r="A43" s="1">
         <v>41</v>
       </c>
@@ -11097,7 +11097,7 @@
         <v>0.54900000000000004</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="29">
+    <row r="44" spans="1:13" ht="30">
       <c r="A44" s="1">
         <v>42</v>
       </c>
@@ -11138,7 +11138,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="29">
+    <row r="45" spans="1:13" ht="30">
       <c r="A45" s="1">
         <v>43</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>0.48480000000000001</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="29">
+    <row r="46" spans="1:13" ht="30">
       <c r="A46" s="1">
         <v>44</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="29">
+    <row r="47" spans="1:13" ht="30">
       <c r="A47" s="1">
         <v>45</v>
       </c>
@@ -11261,7 +11261,7 @@
         <v>0.86360000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="29">
+    <row r="48" spans="1:13" ht="30">
       <c r="A48" s="1">
         <v>46</v>
       </c>
@@ -11302,7 +11302,7 @@
         <v>0.68420000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:13" ht="43.5">
+    <row r="49" spans="1:13" ht="45">
       <c r="A49" s="1">
         <v>47</v>
       </c>
@@ -11343,7 +11343,7 @@
         <v>0.22539999999999999</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="29">
+    <row r="50" spans="1:13" ht="45">
       <c r="A50" s="1">
         <v>48</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>0.73470000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="29">
+    <row r="51" spans="1:13" ht="30">
       <c r="A51" s="1">
         <v>49</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="43.5">
+    <row r="52" spans="1:13" ht="45">
       <c r="A52" s="1">
         <v>50</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>0.81630000000000003</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="29">
+    <row r="53" spans="1:13" ht="30">
       <c r="A53" s="1">
         <v>51</v>
       </c>
@@ -11507,7 +11507,7 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="43.5">
+    <row r="54" spans="1:13" ht="45">
       <c r="A54" s="1">
         <v>52</v>
       </c>
@@ -11548,7 +11548,7 @@
         <v>0.69089999999999996</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="43.5">
+    <row r="55" spans="1:13" ht="45">
       <c r="A55" s="1">
         <v>53</v>
       </c>
@@ -11589,7 +11589,7 @@
         <v>0.70589999999999997</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="29">
+    <row r="56" spans="1:13" ht="30">
       <c r="A56" s="1">
         <v>54</v>
       </c>
@@ -11671,7 +11671,7 @@
         <v>0.47060000000000002</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="29">
+    <row r="58" spans="1:13" ht="30">
       <c r="A58" s="1">
         <v>56</v>
       </c>
@@ -11712,7 +11712,7 @@
         <v>0.76470000000000005</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="43.5">
+    <row r="59" spans="1:13" ht="45">
       <c r="A59" s="1">
         <v>57</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="43.5">
+    <row r="62" spans="1:13" ht="60">
       <c r="A62" s="1">
         <v>60</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>0.7419</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="29">
+    <row r="63" spans="1:13" ht="30">
       <c r="A63" s="1">
         <v>61</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>0.69769999999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="29">
+    <row r="64" spans="1:13" ht="30">
       <c r="A64" s="1">
         <v>62</v>
       </c>
@@ -11958,7 +11958,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="29">
+    <row r="65" spans="1:13" ht="30">
       <c r="A65" s="1">
         <v>63</v>
       </c>
@@ -11999,7 +11999,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="43.5">
+    <row r="66" spans="1:13" ht="45">
       <c r="A66" s="1">
         <v>64</v>
       </c>
@@ -12040,7 +12040,7 @@
         <v>0.61819999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="29">
+    <row r="67" spans="1:13" ht="30">
       <c r="A67" s="1">
         <v>65</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="43.5">
+    <row r="68" spans="1:13" ht="45">
       <c r="A68" s="1">
         <v>66</v>
       </c>
@@ -12122,7 +12122,7 @@
         <v>0.58819999999999995</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="29">
+    <row r="69" spans="1:13" ht="30">
       <c r="A69" s="1">
         <v>67</v>
       </c>
@@ -12163,7 +12163,7 @@
         <v>0.53849999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="29">
+    <row r="70" spans="1:13" ht="30">
       <c r="A70" s="1">
         <v>68</v>
       </c>
@@ -12245,7 +12245,7 @@
         <v>0.63160000000000005</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="58">
+    <row r="72" spans="1:13" ht="60">
       <c r="A72" s="1">
         <v>70</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="101.5">
+    <row r="73" spans="1:13" ht="120">
       <c r="A73" s="1">
         <v>71</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>0.42499999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="43.5">
+    <row r="74" spans="1:13" ht="45">
       <c r="A74" s="1">
         <v>72</v>
       </c>
@@ -12368,7 +12368,7 @@
         <v>0.7843</v>
       </c>
     </row>
-    <row r="75" spans="1:13" ht="43.5">
+    <row r="75" spans="1:13" ht="45">
       <c r="A75" s="1">
         <v>73</v>
       </c>
@@ -12409,7 +12409,7 @@
         <v>0.71699999999999997</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="29">
+    <row r="76" spans="1:13" ht="30">
       <c r="A76" s="1">
         <v>74</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="77" spans="1:13" ht="43.5">
+    <row r="77" spans="1:13" ht="45">
       <c r="A77" s="1">
         <v>75</v>
       </c>
@@ -12491,7 +12491,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="29">
+    <row r="78" spans="1:13" ht="30">
       <c r="A78" s="1">
         <v>76</v>
       </c>
@@ -12573,7 +12573,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="80" spans="1:13" ht="29">
+    <row r="80" spans="1:13" ht="30">
       <c r="A80" s="1">
         <v>78</v>
       </c>
@@ -12614,7 +12614,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="81" spans="1:13" ht="29">
+    <row r="81" spans="1:13" ht="30">
       <c r="A81" s="1">
         <v>79</v>
       </c>
@@ -12655,7 +12655,7 @@
         <v>0.48280000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:13" ht="29">
+    <row r="82" spans="1:13" ht="30">
       <c r="A82" s="1">
         <v>80</v>
       </c>
@@ -12696,7 +12696,7 @@
         <v>0.58330000000000004</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="29">
+    <row r="83" spans="1:13" ht="30">
       <c r="A83" s="1">
         <v>81</v>
       </c>
@@ -12778,7 +12778,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="29">
+    <row r="85" spans="1:13" ht="30">
       <c r="A85" s="1">
         <v>83</v>
       </c>
@@ -12819,7 +12819,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="29">
+    <row r="86" spans="1:13" ht="30">
       <c r="A86" s="1">
         <v>84</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="87" spans="1:13" ht="29">
+    <row r="87" spans="1:13" ht="30">
       <c r="A87" s="1">
         <v>85</v>
       </c>
@@ -12901,7 +12901,7 @@
         <v>0.77780000000000005</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="29">
+    <row r="88" spans="1:13" ht="30">
       <c r="A88" s="1">
         <v>86</v>
       </c>
@@ -12942,7 +12942,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="29">
+    <row r="89" spans="1:13" ht="30">
       <c r="A89" s="1">
         <v>87</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>0.70589999999999997</v>
       </c>
     </row>
-    <row r="90" spans="1:13" ht="29">
+    <row r="90" spans="1:13" ht="30">
       <c r="A90" s="1">
         <v>88</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>0.68969999999999998</v>
       </c>
     </row>
-    <row r="91" spans="1:13" ht="29">
+    <row r="91" spans="1:13" ht="30">
       <c r="A91" s="1">
         <v>89</v>
       </c>
@@ -13065,7 +13065,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="29">
+    <row r="92" spans="1:13" ht="30">
       <c r="A92" s="1">
         <v>90</v>
       </c>
@@ -13147,7 +13147,7 @@
         <v>0.76190000000000002</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="29">
+    <row r="94" spans="1:13" ht="30">
       <c r="A94" s="1">
         <v>92</v>
       </c>
@@ -13188,7 +13188,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="29">
+    <row r="95" spans="1:13" ht="30">
       <c r="A95" s="1">
         <v>93</v>
       </c>
@@ -13270,7 +13270,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="97" spans="1:13" ht="29">
+    <row r="97" spans="1:13" ht="30">
       <c r="A97" s="1">
         <v>95</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="29">
+    <row r="98" spans="1:13" ht="30">
       <c r="A98" s="1">
         <v>96</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>0.7097</v>
       </c>
     </row>
-    <row r="99" spans="1:13" ht="29">
+    <row r="99" spans="1:13" ht="30">
       <c r="A99" s="1">
         <v>97</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>0.63160000000000005</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="29">
+    <row r="100" spans="1:13" ht="30">
       <c r="A100" s="1">
         <v>98</v>
       </c>
@@ -13434,7 +13434,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="29">
+    <row r="101" spans="1:13" ht="30">
       <c r="A101" s="1">
         <v>99</v>
       </c>
@@ -13475,7 +13475,7 @@
         <v>0.76190000000000002</v>
       </c>
     </row>
-    <row r="102" spans="1:13" ht="29">
+    <row r="102" spans="1:13" ht="30">
       <c r="A102" s="1">
         <v>100</v>
       </c>
@@ -13557,7 +13557,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="104" spans="1:13">
+    <row r="104" spans="1:13" ht="30">
       <c r="A104" s="1">
         <v>102</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="29">
+    <row r="105" spans="1:13" ht="30">
       <c r="A105" s="1">
         <v>103</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>0.78569999999999995</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="29">
+    <row r="106" spans="1:13" ht="30">
       <c r="A106" s="1">
         <v>104</v>
       </c>
@@ -13680,7 +13680,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="29">
+    <row r="107" spans="1:13" ht="30">
       <c r="A107" s="1">
         <v>105</v>
       </c>
@@ -13721,7 +13721,7 @@
         <v>0.58540000000000003</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="29">
+    <row r="108" spans="1:13" ht="30">
       <c r="A108" s="1">
         <v>106</v>
       </c>
@@ -13803,7 +13803,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:13" ht="29">
+    <row r="110" spans="1:13" ht="30">
       <c r="A110" s="1">
         <v>108</v>
       </c>
@@ -13844,7 +13844,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="111" spans="1:13" ht="29">
+    <row r="111" spans="1:13" ht="30">
       <c r="A111" s="1">
         <v>109</v>
       </c>
@@ -13885,7 +13885,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="112" spans="1:13" ht="29">
+    <row r="112" spans="1:13" ht="30">
       <c r="A112" s="1">
         <v>110</v>
       </c>
@@ -13926,7 +13926,7 @@
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="113" spans="1:13" ht="29">
+    <row r="113" spans="1:13" ht="30">
       <c r="A113" s="1">
         <v>111</v>
       </c>
@@ -13967,7 +13967,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="29">
+    <row r="114" spans="1:13" ht="30">
       <c r="A114" s="1">
         <v>112</v>
       </c>
@@ -14008,7 +14008,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="58">
+    <row r="115" spans="1:13" ht="60">
       <c r="A115" s="1">
         <v>113</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="29">
+    <row r="117" spans="1:13" ht="30">
       <c r="A117" s="1">
         <v>115</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="29">
+    <row r="118" spans="1:13" ht="30">
       <c r="A118" s="1">
         <v>116</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="119" spans="1:13" ht="29">
+    <row r="119" spans="1:13" ht="30">
       <c r="A119" s="1">
         <v>117</v>
       </c>
@@ -14211,7 +14211,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="58">
+    <row r="120" spans="1:13" ht="60">
       <c r="A120" s="1">
         <v>118</v>
       </c>
@@ -14252,7 +14252,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="121" spans="1:13" ht="29">
+    <row r="121" spans="1:13" ht="30">
       <c r="A121" s="1">
         <v>119</v>
       </c>
@@ -14293,7 +14293,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="122" spans="1:13" ht="29">
+    <row r="122" spans="1:13" ht="30">
       <c r="A122" s="1">
         <v>120</v>
       </c>
@@ -14375,7 +14375,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="29">
+    <row r="124" spans="1:13" ht="30">
       <c r="A124" s="1">
         <v>122</v>
       </c>
@@ -14416,7 +14416,7 @@
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="125" spans="1:13">
+    <row r="125" spans="1:13" ht="30">
       <c r="A125" s="1">
         <v>123</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>0.76190000000000002</v>
       </c>
     </row>
-    <row r="127" spans="1:13" ht="29">
+    <row r="127" spans="1:13" ht="30">
       <c r="A127" s="1">
         <v>125</v>
       </c>
@@ -14539,7 +14539,7 @@
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="128" spans="1:13" ht="58">
+    <row r="128" spans="1:13" ht="60">
       <c r="A128" s="1">
         <v>126</v>
       </c>
@@ -14580,7 +14580,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="29">
+    <row r="129" spans="1:13" ht="30">
       <c r="A129" s="1">
         <v>127</v>
       </c>
@@ -14621,7 +14621,7 @@
         <v>0.89659999999999995</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="29">
+    <row r="130" spans="1:13" ht="30">
       <c r="A130" s="1">
         <v>128</v>
       </c>
@@ -14662,7 +14662,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="131" spans="1:13" ht="58">
+    <row r="131" spans="1:13" ht="60">
       <c r="A131" s="1">
         <v>129</v>
       </c>
@@ -14703,7 +14703,7 @@
         <v>0.82350000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="29">
+    <row r="132" spans="1:13" ht="30">
       <c r="A132" s="1">
         <v>130</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="133" spans="1:13" ht="29">
+    <row r="133" spans="1:13" ht="30">
       <c r="A133" s="1">
         <v>131</v>
       </c>
@@ -14785,7 +14785,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="134" spans="1:13" ht="29">
+    <row r="134" spans="1:13" ht="30">
       <c r="A134" s="1">
         <v>132</v>
       </c>
@@ -14826,7 +14826,7 @@
         <v>0.51849999999999996</v>
       </c>
     </row>
-    <row r="135" spans="1:13">
+    <row r="135" spans="1:13" ht="30">
       <c r="A135" s="1">
         <v>133</v>
       </c>
@@ -14867,7 +14867,7 @@
         <v>0.45450000000000002</v>
       </c>
     </row>
-    <row r="136" spans="1:13">
+    <row r="136" spans="1:13" ht="30">
       <c r="A136" s="1">
         <v>134</v>
       </c>
@@ -14908,7 +14908,7 @@
         <v>0.55559999999999998</v>
       </c>
     </row>
-    <row r="137" spans="1:13">
+    <row r="137" spans="1:13" ht="30">
       <c r="A137" s="1">
         <v>135</v>
       </c>
@@ -14949,7 +14949,7 @@
         <v>0.44440000000000002</v>
       </c>
     </row>
-    <row r="138" spans="1:13" ht="29">
+    <row r="138" spans="1:13" ht="30">
       <c r="A138" s="1">
         <v>136</v>
       </c>
@@ -14990,7 +14990,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="29">
+    <row r="139" spans="1:13" ht="30">
       <c r="A139" s="1">
         <v>137</v>
       </c>
@@ -15031,7 +15031,7 @@
         <v>0.44440000000000002</v>
       </c>
     </row>
-    <row r="140" spans="1:13" ht="29">
+    <row r="140" spans="1:13" ht="30">
       <c r="A140" s="1">
         <v>138</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>0.52939999999999998</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="29">
+    <row r="141" spans="1:13" ht="30">
       <c r="A141" s="1">
         <v>139</v>
       </c>
@@ -15113,7 +15113,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="142" spans="1:13" ht="29">
+    <row r="142" spans="1:13" ht="30">
       <c r="A142" s="1">
         <v>140</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:13">
+    <row r="143" spans="1:13" ht="30">
       <c r="A143" s="1">
         <v>141</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>0.55559999999999998</v>
       </c>
     </row>
-    <row r="144" spans="1:13">
+    <row r="144" spans="1:13" ht="30">
       <c r="A144" s="1">
         <v>142</v>
       </c>
@@ -15277,7 +15277,7 @@
         <v>0.47060000000000002</v>
       </c>
     </row>
-    <row r="146" spans="1:13">
+    <row r="146" spans="1:13" ht="30">
       <c r="A146" s="1">
         <v>144</v>
       </c>
@@ -15318,7 +15318,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="147" spans="1:13">
+    <row r="147" spans="1:13" ht="30">
       <c r="A147" s="1">
         <v>145</v>
       </c>
@@ -15400,7 +15400,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="29">
+    <row r="149" spans="1:13" ht="30">
       <c r="A149" s="1">
         <v>147</v>
       </c>
@@ -15441,7 +15441,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="29">
+    <row r="150" spans="1:13" ht="30">
       <c r="A150" s="1">
         <v>148</v>
       </c>
@@ -15482,7 +15482,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="29">
+    <row r="151" spans="1:13" ht="30">
       <c r="A151" s="1">
         <v>149</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>0.58819999999999995</v>
       </c>
     </row>
-    <row r="156" spans="1:13">
+    <row r="156" spans="1:13" ht="30">
       <c r="A156" s="1">
         <v>154</v>
       </c>
@@ -15728,7 +15728,7 @@
         <v>0.45450000000000002</v>
       </c>
     </row>
-    <row r="157" spans="1:13" ht="29">
+    <row r="157" spans="1:13" ht="30">
       <c r="A157" s="1">
         <v>155</v>
       </c>
@@ -15769,7 +15769,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="158" spans="1:13">
+    <row r="158" spans="1:13" ht="30">
       <c r="A158" s="1">
         <v>156</v>
       </c>
@@ -15810,7 +15810,7 @@
         <v>0.42109999999999997</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="29">
+    <row r="159" spans="1:13" ht="30">
       <c r="A159" s="1">
         <v>157</v>
       </c>
@@ -15851,7 +15851,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="29">
+    <row r="160" spans="1:13" ht="30">
       <c r="A160" s="1">
         <v>158</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="161" spans="1:13" ht="29">
+    <row r="161" spans="1:13" ht="30">
       <c r="A161" s="1">
         <v>159</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="29">
+    <row r="171" spans="1:13" ht="30">
       <c r="A171" s="1">
         <v>169</v>
       </c>
@@ -16341,7 +16341,7 @@
         <v>0.56410000000000005</v>
       </c>
     </row>
-    <row r="172" spans="1:13" ht="29">
+    <row r="172" spans="1:13" ht="30">
       <c r="A172" s="1">
         <v>170</v>
       </c>
@@ -16382,7 +16382,7 @@
         <v>0.69569999999999999</v>
       </c>
     </row>
-    <row r="173" spans="1:13" ht="29">
+    <row r="173" spans="1:13" ht="30">
       <c r="A173" s="1">
         <v>171</v>
       </c>
@@ -16423,7 +16423,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="174" spans="1:13" ht="43.5">
+    <row r="174" spans="1:13" ht="45">
       <c r="A174" s="1">
         <v>172</v>
       </c>
@@ -16546,7 +16546,7 @@
         <v>0.26669999999999999</v>
       </c>
     </row>
-    <row r="177" spans="1:13" ht="29">
+    <row r="177" spans="1:13" ht="30">
       <c r="A177" s="1">
         <v>175</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="181" spans="1:13" ht="29">
+    <row r="181" spans="1:13" ht="30">
       <c r="A181" s="1">
         <v>179</v>
       </c>
@@ -16788,7 +16788,7 @@
         <v>0.47060000000000002</v>
       </c>
     </row>
-    <row r="183" spans="1:13" ht="43.5">
+    <row r="183" spans="1:13" ht="45">
       <c r="A183" s="1">
         <v>181</v>
       </c>
@@ -16829,7 +16829,7 @@
         <v>0.6552</v>
       </c>
     </row>
-    <row r="184" spans="1:13" ht="43.5">
+    <row r="184" spans="1:13" ht="45">
       <c r="A184" s="1">
         <v>182</v>
       </c>
@@ -16870,7 +16870,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="185" spans="1:13" ht="43.5">
+    <row r="185" spans="1:13" ht="45">
       <c r="A185" s="1">
         <v>183</v>
       </c>
@@ -16911,7 +16911,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="186" spans="1:13" ht="43.5">
+    <row r="186" spans="1:13" ht="45">
       <c r="A186" s="1">
         <v>184</v>
       </c>
@@ -16952,7 +16952,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="187" spans="1:13" ht="29">
+    <row r="187" spans="1:13" ht="45">
       <c r="A187" s="1">
         <v>185</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="188" spans="1:13" ht="29">
+    <row r="188" spans="1:13" ht="30">
       <c r="A188" s="1">
         <v>186</v>
       </c>
@@ -17034,7 +17034,7 @@
         <v>0.6038</v>
       </c>
     </row>
-    <row r="189" spans="1:13" ht="29">
+    <row r="189" spans="1:13" ht="30">
       <c r="A189" s="1">
         <v>187</v>
       </c>
@@ -17075,7 +17075,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="190" spans="1:13" ht="29">
+    <row r="190" spans="1:13" ht="30">
       <c r="A190" s="1">
         <v>188</v>
       </c>
@@ -17116,7 +17116,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="191" spans="1:13" ht="29">
+    <row r="191" spans="1:13" ht="45">
       <c r="A191" s="1">
         <v>189</v>
       </c>
@@ -17198,7 +17198,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="193" spans="1:13" ht="29">
+    <row r="193" spans="1:13" ht="30">
       <c r="A193" s="1">
         <v>191</v>
       </c>
@@ -17280,7 +17280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:13" ht="29">
+    <row r="195" spans="1:13" ht="30">
       <c r="A195" s="1">
         <v>193</v>
       </c>
@@ -17403,7 +17403,7 @@
         <v>0.84209999999999996</v>
       </c>
     </row>
-    <row r="198" spans="1:13" ht="29">
+    <row r="198" spans="1:13" ht="30">
       <c r="A198" s="1">
         <v>196</v>
       </c>
@@ -17444,7 +17444,7 @@
         <v>0.78569999999999995</v>
       </c>
     </row>
-    <row r="199" spans="1:13" ht="29">
+    <row r="199" spans="1:13" ht="30">
       <c r="A199" s="1">
         <v>197</v>
       </c>
@@ -17567,7 +17567,7 @@
         <v>0.95240000000000002</v>
       </c>
     </row>
-    <row r="202" spans="1:13">
+    <row r="202" spans="1:13" ht="30">
       <c r="A202" s="1">
         <v>200</v>
       </c>
@@ -17608,7 +17608,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="203" spans="1:13">
+    <row r="203" spans="1:13" ht="30">
       <c r="A203" s="1">
         <v>201</v>
       </c>
@@ -17645,7 +17645,7 @@
         <v>0.69569999999999999</v>
       </c>
     </row>
-    <row r="204" spans="1:13" ht="29">
+    <row r="204" spans="1:13" ht="30">
       <c r="A204" s="1">
         <v>202</v>
       </c>
@@ -17830,7 +17830,7 @@
         <v>0.76190000000000002</v>
       </c>
     </row>
-    <row r="209" spans="1:13" ht="29">
+    <row r="209" spans="1:13" ht="30">
       <c r="A209" s="1">
         <v>207</v>
       </c>
@@ -17867,7 +17867,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="210" spans="1:13" ht="29">
+    <row r="210" spans="1:13" ht="30">
       <c r="A210" s="1">
         <v>208</v>
       </c>
@@ -17904,7 +17904,7 @@
         <v>0.84850000000000003</v>
       </c>
     </row>
-    <row r="211" spans="1:13" ht="43.5">
+    <row r="211" spans="1:13" ht="45">
       <c r="A211" s="1">
         <v>209</v>
       </c>
@@ -17941,7 +17941,7 @@
         <v>0.68969999999999998</v>
       </c>
     </row>
-    <row r="212" spans="1:13" ht="58">
+    <row r="212" spans="1:13" ht="60">
       <c r="A212" s="1">
         <v>210</v>
       </c>
@@ -17978,7 +17978,7 @@
         <v>0.73170000000000002</v>
       </c>
     </row>
-    <row r="213" spans="1:13">
+    <row r="213" spans="1:13" ht="30">
       <c r="A213" s="1">
         <v>211</v>
       </c>
@@ -18015,7 +18015,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="214" spans="1:13" ht="29">
+    <row r="214" spans="1:13" ht="30">
       <c r="A214" s="1">
         <v>212</v>
       </c>
@@ -18052,7 +18052,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="215" spans="1:13" ht="29">
+    <row r="215" spans="1:13" ht="30">
       <c r="A215" s="1">
         <v>213</v>
       </c>
@@ -18089,7 +18089,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="216" spans="1:13">
+    <row r="216" spans="1:13" ht="30">
       <c r="A216" s="1">
         <v>214</v>
       </c>
@@ -18126,7 +18126,7 @@
         <v>0.86960000000000004</v>
       </c>
     </row>
-    <row r="217" spans="1:13" ht="29">
+    <row r="217" spans="1:13" ht="30">
       <c r="A217" s="1">
         <v>215</v>
       </c>
@@ -18163,7 +18163,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="218" spans="1:13" ht="29">
+    <row r="218" spans="1:13" ht="30">
       <c r="A218" s="1">
         <v>216</v>
       </c>
@@ -18200,7 +18200,7 @@
         <v>0.7097</v>
       </c>
     </row>
-    <row r="219" spans="1:13" ht="29">
+    <row r="219" spans="1:13" ht="30">
       <c r="A219" s="1">
         <v>217</v>
       </c>
@@ -18237,7 +18237,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="220" spans="1:13" ht="29">
+    <row r="220" spans="1:13" ht="30">
       <c r="A220" s="1">
         <v>218</v>
       </c>
@@ -18274,7 +18274,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="221" spans="1:13" ht="29">
+    <row r="221" spans="1:13" ht="30">
       <c r="A221" s="1">
         <v>219</v>
       </c>
@@ -18311,7 +18311,7 @@
         <v>0.84619999999999995</v>
       </c>
     </row>
-    <row r="222" spans="1:13" ht="29">
+    <row r="222" spans="1:13" ht="30">
       <c r="A222" s="1">
         <v>220</v>
       </c>
@@ -18348,7 +18348,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="223" spans="1:13" ht="29">
+    <row r="223" spans="1:13" ht="30">
       <c r="A223" s="1">
         <v>221</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="224" spans="1:13" ht="29">
+    <row r="224" spans="1:13" ht="30">
       <c r="A224" s="1">
         <v>222</v>
       </c>
@@ -18422,7 +18422,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="225" spans="1:13" ht="29">
+    <row r="225" spans="1:13" ht="30">
       <c r="A225" s="1">
         <v>223</v>
       </c>
@@ -18496,7 +18496,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="227" spans="1:13">
+    <row r="227" spans="1:13" ht="30">
       <c r="A227" s="1">
         <v>225</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="229" spans="1:13" ht="29">
+    <row r="229" spans="1:13" ht="30">
       <c r="A229" s="1">
         <v>227</v>
       </c>
@@ -18607,7 +18607,7 @@
         <v>0.69569999999999999</v>
       </c>
     </row>
-    <row r="230" spans="1:13" ht="29">
+    <row r="230" spans="1:13" ht="30">
       <c r="A230" s="1">
         <v>228</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>0.83720000000000006</v>
       </c>
     </row>
-    <row r="231" spans="1:13" ht="29">
+    <row r="231" spans="1:13" ht="30">
       <c r="A231" s="1">
         <v>229</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="232" spans="1:13" ht="29">
+    <row r="232" spans="1:13" ht="30">
       <c r="A232" s="1">
         <v>230</v>
       </c>
@@ -18718,7 +18718,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="233" spans="1:13" ht="29">
+    <row r="233" spans="1:13" ht="30">
       <c r="A233" s="1">
         <v>231</v>
       </c>
@@ -18755,7 +18755,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="234" spans="1:13" ht="29">
+    <row r="234" spans="1:13" ht="30">
       <c r="A234" s="1">
         <v>232</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>0.86960000000000004</v>
       </c>
     </row>
-    <row r="235" spans="1:13" ht="29">
+    <row r="235" spans="1:13" ht="30">
       <c r="A235" s="1">
         <v>233</v>
       </c>
@@ -18866,7 +18866,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="237" spans="1:13" ht="29">
+    <row r="237" spans="1:13" ht="30">
       <c r="A237" s="1">
         <v>235</v>
       </c>
@@ -18903,7 +18903,7 @@
         <v>0.91669999999999996</v>
       </c>
     </row>
-    <row r="238" spans="1:13" ht="29">
+    <row r="238" spans="1:13" ht="30">
       <c r="A238" s="1">
         <v>236</v>
       </c>
@@ -18940,7 +18940,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="239" spans="1:13">
+    <row r="239" spans="1:13" ht="30">
       <c r="A239" s="1">
         <v>237</v>
       </c>
@@ -19014,7 +19014,7 @@
         <v>0.95240000000000002</v>
       </c>
     </row>
-    <row r="241" spans="1:13" ht="29">
+    <row r="241" spans="1:13" ht="30">
       <c r="A241" s="1">
         <v>239</v>
       </c>
@@ -19051,7 +19051,7 @@
         <v>0.8387</v>
       </c>
     </row>
-    <row r="242" spans="1:13">
+    <row r="242" spans="1:13" ht="30">
       <c r="A242" s="1">
         <v>240</v>
       </c>
@@ -19088,7 +19088,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="243" spans="1:13" ht="29">
+    <row r="243" spans="1:13" ht="30">
       <c r="A243" s="1">
         <v>241</v>
       </c>
@@ -19125,7 +19125,7 @@
         <v>0.86960000000000004</v>
       </c>
     </row>
-    <row r="244" spans="1:13" ht="29">
+    <row r="244" spans="1:13" ht="30">
       <c r="A244" s="1">
         <v>242</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>0.94120000000000004</v>
       </c>
     </row>
-    <row r="245" spans="1:13" ht="29">
+    <row r="245" spans="1:13" ht="30">
       <c r="A245" s="1">
         <v>243</v>
       </c>
@@ -19199,7 +19199,7 @@
         <v>0.6512</v>
       </c>
     </row>
-    <row r="246" spans="1:13" ht="29">
+    <row r="246" spans="1:13" ht="30">
       <c r="A246" s="1">
         <v>244</v>
       </c>
@@ -19236,7 +19236,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="247" spans="1:13" ht="29">
+    <row r="247" spans="1:13" ht="30">
       <c r="A247" s="1">
         <v>245</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="248" spans="1:13" ht="29">
+    <row r="248" spans="1:13" ht="30">
       <c r="A248" s="1">
         <v>246</v>
       </c>
@@ -19310,7 +19310,7 @@
         <v>0.7742</v>
       </c>
     </row>
-    <row r="249" spans="1:13">
+    <row r="249" spans="1:13" ht="30">
       <c r="A249" s="1">
         <v>247</v>
       </c>
@@ -19347,7 +19347,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="250" spans="1:13">
+    <row r="250" spans="1:13" ht="30">
       <c r="A250" s="1">
         <v>248</v>
       </c>
@@ -19384,7 +19384,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="251" spans="1:13" ht="29">
+    <row r="251" spans="1:13" ht="30">
       <c r="A251" s="1">
         <v>249</v>
       </c>
@@ -19421,7 +19421,7 @@
         <v>0.93330000000000002</v>
       </c>
     </row>
-    <row r="252" spans="1:13" ht="29">
+    <row r="252" spans="1:13" ht="30">
       <c r="A252" s="1">
         <v>250</v>
       </c>
@@ -19458,7 +19458,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="253" spans="1:13">
+    <row r="253" spans="1:13" ht="30">
       <c r="A253" s="1">
         <v>251</v>
       </c>
@@ -19495,7 +19495,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="254" spans="1:13" ht="29">
+    <row r="254" spans="1:13" ht="30">
       <c r="A254" s="1">
         <v>252</v>
       </c>
@@ -19532,7 +19532,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="255" spans="1:13">
+    <row r="255" spans="1:13" ht="30">
       <c r="A255" s="1">
         <v>253</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="256" spans="1:13">
+    <row r="256" spans="1:13" ht="30">
       <c r="A256" s="1">
         <v>254</v>
       </c>
@@ -19717,7 +19717,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:13">
+    <row r="260" spans="1:13" ht="30">
       <c r="A260" s="1">
         <v>258</v>
       </c>
@@ -19754,7 +19754,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="29">
+    <row r="261" spans="1:13" ht="30">
       <c r="A261" s="1">
         <v>259</v>
       </c>
@@ -19791,7 +19791,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="262" spans="1:13">
+    <row r="262" spans="1:13" ht="30">
       <c r="A262" s="1">
         <v>260</v>
       </c>
@@ -19939,7 +19939,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="266" spans="1:13" ht="29">
+    <row r="266" spans="1:13" ht="30">
       <c r="A266" s="1">
         <v>264</v>
       </c>
@@ -19976,7 +19976,7 @@
         <v>0.60870000000000002</v>
       </c>
     </row>
-    <row r="267" spans="1:13" ht="29">
+    <row r="267" spans="1:13" ht="30">
       <c r="A267" s="1">
         <v>265</v>
       </c>
@@ -20087,7 +20087,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="270" spans="1:13" ht="29">
+    <row r="270" spans="1:13" ht="30">
       <c r="A270" s="1">
         <v>268</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>0.55169999999999997</v>
       </c>
     </row>
-    <row r="271" spans="1:13" ht="29">
+    <row r="271" spans="1:13" ht="30">
       <c r="A271" s="1">
         <v>269</v>
       </c>
@@ -20161,7 +20161,7 @@
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="272" spans="1:13" ht="29">
+    <row r="272" spans="1:13" ht="30">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -20198,7 +20198,7 @@
         <v>0.5625</v>
       </c>
     </row>
-    <row r="273" spans="1:13" ht="29">
+    <row r="273" spans="1:13" ht="45">
       <c r="A273" s="1">
         <v>271</v>
       </c>
@@ -20235,7 +20235,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="274" spans="1:13" ht="43.5">
+    <row r="274" spans="1:13" ht="45">
       <c r="A274" s="1">
         <v>272</v>
       </c>
@@ -20272,7 +20272,7 @@
         <v>0.65620000000000001</v>
       </c>
     </row>
-    <row r="275" spans="1:13" ht="29">
+    <row r="275" spans="1:13" ht="30">
       <c r="A275" s="1">
         <v>273</v>
       </c>
@@ -20309,7 +20309,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="276" spans="1:13" ht="29">
+    <row r="276" spans="1:13" ht="30">
       <c r="A276" s="1">
         <v>274</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="277" spans="1:13" ht="29">
+    <row r="277" spans="1:13" ht="30">
       <c r="A277" s="1">
         <v>275</v>
       </c>
@@ -20383,7 +20383,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="278" spans="1:13" ht="29">
+    <row r="278" spans="1:13" ht="30">
       <c r="A278" s="1">
         <v>276</v>
       </c>
@@ -20420,7 +20420,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="279" spans="1:13" ht="29">
+    <row r="279" spans="1:13" ht="30">
       <c r="A279" s="1">
         <v>277</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>0.68289999999999995</v>
       </c>
     </row>
-    <row r="280" spans="1:13" ht="29">
+    <row r="280" spans="1:13" ht="30">
       <c r="A280" s="1">
         <v>278</v>
       </c>
@@ -20494,7 +20494,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="281" spans="1:13" ht="43.5">
+    <row r="281" spans="1:13" ht="45">
       <c r="A281" s="1">
         <v>279</v>
       </c>
@@ -20531,7 +20531,7 @@
         <v>0.57779999999999998</v>
       </c>
     </row>
-    <row r="282" spans="1:13" ht="43.5">
+    <row r="282" spans="1:13" ht="45">
       <c r="A282" s="1">
         <v>280</v>
       </c>
@@ -20568,7 +20568,7 @@
         <v>0.81630000000000003</v>
       </c>
     </row>
-    <row r="283" spans="1:13" ht="29">
+    <row r="283" spans="1:13" ht="30">
       <c r="A283" s="1">
         <v>281</v>
       </c>
@@ -20605,7 +20605,7 @@
         <v>0.58540000000000003</v>
       </c>
     </row>
-    <row r="284" spans="1:13">
+    <row r="284" spans="1:13" ht="30">
       <c r="A284" s="1">
         <v>282</v>
       </c>
@@ -20642,7 +20642,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="285" spans="1:13" ht="29">
+    <row r="285" spans="1:13" ht="45">
       <c r="A285" s="1">
         <v>283</v>
       </c>
@@ -20679,7 +20679,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="286" spans="1:13" ht="72.5">
+    <row r="286" spans="1:13" ht="75">
       <c r="A286" s="1">
         <v>284</v>
       </c>
@@ -20716,7 +20716,7 @@
         <v>0.6038</v>
       </c>
     </row>
-    <row r="287" spans="1:13" ht="29">
+    <row r="287" spans="1:13" ht="30">
       <c r="A287" s="1">
         <v>285</v>
       </c>
@@ -20753,7 +20753,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="288" spans="1:13" ht="29">
+    <row r="288" spans="1:13" ht="30">
       <c r="A288" s="1">
         <v>286</v>
       </c>
@@ -20790,7 +20790,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="289" spans="1:13" ht="29">
+    <row r="289" spans="1:13" ht="30">
       <c r="A289" s="1">
         <v>287</v>
       </c>
@@ -20827,7 +20827,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="290" spans="1:13" ht="29">
+    <row r="290" spans="1:13" ht="30">
       <c r="A290" s="1">
         <v>288</v>
       </c>
@@ -20864,7 +20864,7 @@
         <v>0.76470000000000005</v>
       </c>
     </row>
-    <row r="291" spans="1:13" ht="29">
+    <row r="291" spans="1:13" ht="30">
       <c r="A291" s="1">
         <v>289</v>
       </c>
@@ -20901,7 +20901,7 @@
         <v>0.87180000000000002</v>
       </c>
     </row>
-    <row r="292" spans="1:13" ht="29">
+    <row r="292" spans="1:13" ht="30">
       <c r="A292" s="1">
         <v>290</v>
       </c>
@@ -20938,7 +20938,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="293" spans="1:13" ht="29">
+    <row r="293" spans="1:13" ht="30">
       <c r="A293" s="1">
         <v>291</v>
       </c>
@@ -20975,7 +20975,7 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="294" spans="1:13" ht="43.5">
+    <row r="294" spans="1:13" ht="45">
       <c r="A294" s="1">
         <v>292</v>
       </c>
@@ -21012,7 +21012,7 @@
         <v>0.72340000000000004</v>
       </c>
     </row>
-    <row r="295" spans="1:13" ht="43.5">
+    <row r="295" spans="1:13" ht="45">
       <c r="A295" s="1">
         <v>293</v>
       </c>
@@ -21049,7 +21049,7 @@
         <v>0.47270000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:13" ht="29">
+    <row r="296" spans="1:13" ht="30">
       <c r="A296" s="1">
         <v>294</v>
       </c>
@@ -21086,7 +21086,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="297" spans="1:13" ht="29">
+    <row r="297" spans="1:13" ht="30">
       <c r="A297" s="1">
         <v>295</v>
       </c>
@@ -21123,7 +21123,7 @@
         <v>0.96299999999999997</v>
       </c>
     </row>
-    <row r="298" spans="1:13" ht="43.5">
+    <row r="298" spans="1:13" ht="45">
       <c r="A298" s="1">
         <v>296</v>
       </c>
@@ -21160,7 +21160,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="299" spans="1:13" ht="29">
+    <row r="299" spans="1:13" ht="30">
       <c r="A299" s="1">
         <v>297</v>
       </c>
@@ -21197,7 +21197,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="300" spans="1:13" ht="29">
+    <row r="300" spans="1:13" ht="30">
       <c r="A300" s="1">
         <v>298</v>
       </c>
@@ -21234,7 +21234,7 @@
         <v>0.68569999999999998</v>
       </c>
     </row>
-    <row r="301" spans="1:13" ht="29">
+    <row r="301" spans="1:13" ht="30">
       <c r="A301" s="1">
         <v>299</v>
       </c>
@@ -21271,7 +21271,7 @@
         <v>0.68420000000000003</v>
       </c>
     </row>
-    <row r="302" spans="1:13" ht="29">
+    <row r="302" spans="1:13" ht="30">
       <c r="A302" s="1">
         <v>300</v>
       </c>
@@ -21308,7 +21308,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="303" spans="1:13" ht="29">
+    <row r="303" spans="1:13" ht="30">
       <c r="A303" s="1">
         <v>301</v>
       </c>
@@ -21345,7 +21345,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="304" spans="1:13" ht="43.5">
+    <row r="304" spans="1:13" ht="45">
       <c r="A304" s="1">
         <v>302</v>
       </c>
@@ -21382,7 +21382,7 @@
         <v>0.4667</v>
       </c>
     </row>
-    <row r="305" spans="1:13" ht="29">
+    <row r="305" spans="1:13" ht="30">
       <c r="A305" s="1">
         <v>303</v>
       </c>
@@ -21419,7 +21419,7 @@
         <v>0.47620000000000001</v>
       </c>
     </row>
-    <row r="306" spans="1:13" ht="29">
+    <row r="306" spans="1:13" ht="30">
       <c r="A306" s="1">
         <v>304</v>
       </c>
@@ -21456,7 +21456,7 @@
         <v>0.68420000000000003</v>
       </c>
     </row>
-    <row r="307" spans="1:13" ht="43.5">
+    <row r="307" spans="1:13" ht="45">
       <c r="A307" s="1">
         <v>305</v>
       </c>
@@ -21493,7 +21493,7 @@
         <v>0.2034</v>
       </c>
     </row>
-    <row r="308" spans="1:13" ht="43.5">
+    <row r="308" spans="1:13" ht="45">
       <c r="A308" s="1">
         <v>306</v>
       </c>
@@ -21530,7 +21530,7 @@
         <v>0.48280000000000001</v>
       </c>
     </row>
-    <row r="309" spans="1:13" ht="29">
+    <row r="309" spans="1:13" ht="30">
       <c r="A309" s="1">
         <v>307</v>
       </c>
@@ -21567,7 +21567,7 @@
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="310" spans="1:13" ht="29">
+    <row r="310" spans="1:13" ht="30">
       <c r="A310" s="1">
         <v>308</v>
       </c>
@@ -21604,7 +21604,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="311" spans="1:13" ht="29">
+    <row r="311" spans="1:13" ht="30">
       <c r="A311" s="1">
         <v>309</v>
       </c>
@@ -21641,7 +21641,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="312" spans="1:13" ht="29">
+    <row r="312" spans="1:13" ht="30">
       <c r="A312" s="1">
         <v>310</v>
       </c>
@@ -21678,7 +21678,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="313" spans="1:13" ht="29">
+    <row r="313" spans="1:13" ht="30">
       <c r="A313" s="1">
         <v>311</v>
       </c>
@@ -21715,7 +21715,7 @@
         <v>0.70589999999999997</v>
       </c>
     </row>
-    <row r="314" spans="1:13" ht="29">
+    <row r="314" spans="1:13" ht="30">
       <c r="A314" s="1">
         <v>312</v>
       </c>
@@ -21752,7 +21752,7 @@
         <v>0.36359999999999998</v>
       </c>
     </row>
-    <row r="315" spans="1:13" ht="29">
+    <row r="315" spans="1:13" ht="45">
       <c r="A315" s="1">
         <v>313</v>
       </c>
@@ -21937,7 +21937,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="320" spans="1:13" ht="29">
+    <row r="320" spans="1:13" ht="45">
       <c r="A320" s="1">
         <v>318</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:13" ht="43.5">
+    <row r="321" spans="1:13" ht="60">
       <c r="A321" s="1">
         <v>319</v>
       </c>
@@ -22011,7 +22011,7 @@
         <v>0.43240000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:13" ht="29">
+    <row r="322" spans="1:13" ht="30">
       <c r="A322" s="1">
         <v>320</v>
       </c>
@@ -22048,7 +22048,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="323" spans="1:13" ht="29">
+    <row r="323" spans="1:13" ht="30">
       <c r="A323" s="1">
         <v>321</v>
       </c>
@@ -22122,7 +22122,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="325" spans="1:13" ht="29">
+    <row r="325" spans="1:13" ht="45">
       <c r="A325" s="1">
         <v>323</v>
       </c>
@@ -22159,7 +22159,7 @@
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="326" spans="1:13" ht="29">
+    <row r="326" spans="1:13" ht="30">
       <c r="A326" s="1">
         <v>324</v>
       </c>
@@ -22196,7 +22196,7 @@
         <v>0.6452</v>
       </c>
     </row>
-    <row r="327" spans="1:13" ht="29">
+    <row r="327" spans="1:13" ht="30">
       <c r="A327" s="1">
         <v>325</v>
       </c>
@@ -22233,7 +22233,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="328" spans="1:13" ht="43.5">
+    <row r="328" spans="1:13" ht="45">
       <c r="A328" s="1">
         <v>326</v>
       </c>
@@ -22270,7 +22270,7 @@
         <v>0.59260000000000002</v>
       </c>
     </row>
-    <row r="329" spans="1:13" ht="29">
+    <row r="329" spans="1:13" ht="30">
       <c r="A329" s="1">
         <v>327</v>
       </c>
@@ -22307,7 +22307,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="330" spans="1:13" ht="58">
+    <row r="330" spans="1:13" ht="60">
       <c r="A330" s="1">
         <v>328</v>
       </c>
@@ -22381,7 +22381,7 @@
         <v>0.47620000000000001</v>
       </c>
     </row>
-    <row r="332" spans="1:13" ht="43.5">
+    <row r="332" spans="1:13" ht="45">
       <c r="A332" s="1">
         <v>330</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="333" spans="1:13" ht="29">
+    <row r="333" spans="1:13" ht="30">
       <c r="A333" s="1">
         <v>331</v>
       </c>
@@ -22455,7 +22455,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="334" spans="1:13" ht="29">
+    <row r="334" spans="1:13" ht="30">
       <c r="A334" s="1">
         <v>332</v>
       </c>
@@ -22492,7 +22492,7 @@
         <v>0.52939999999999998</v>
       </c>
     </row>
-    <row r="335" spans="1:13" ht="43.5">
+    <row r="335" spans="1:13" ht="45">
       <c r="A335" s="1">
         <v>333</v>
       </c>
@@ -22529,7 +22529,7 @@
         <v>0.75470000000000004</v>
       </c>
     </row>
-    <row r="336" spans="1:13" ht="43.5">
+    <row r="336" spans="1:13" ht="45">
       <c r="A336" s="1">
         <v>334</v>
       </c>
@@ -22566,7 +22566,7 @@
         <v>0.7843</v>
       </c>
     </row>
-    <row r="337" spans="1:13" ht="58">
+    <row r="337" spans="1:13" ht="60">
       <c r="A337" s="1">
         <v>335</v>
       </c>
@@ -22603,7 +22603,7 @@
         <v>0.77780000000000005</v>
       </c>
     </row>
-    <row r="338" spans="1:13" ht="43.5">
+    <row r="338" spans="1:13" ht="45">
       <c r="A338" s="1">
         <v>336</v>
       </c>
@@ -22640,7 +22640,7 @@
         <v>0.80700000000000005</v>
       </c>
     </row>
-    <row r="339" spans="1:13" ht="43.5">
+    <row r="339" spans="1:13" ht="60">
       <c r="A339" s="1">
         <v>337</v>
       </c>
@@ -22677,7 +22677,7 @@
         <v>0.82540000000000002</v>
       </c>
     </row>
-    <row r="340" spans="1:13" ht="43.5">
+    <row r="340" spans="1:13" ht="45">
       <c r="A340" s="1">
         <v>338</v>
       </c>
@@ -22714,7 +22714,7 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="341" spans="1:13" ht="43.5">
+    <row r="341" spans="1:13" ht="60">
       <c r="A341" s="1">
         <v>339</v>
       </c>
@@ -22751,7 +22751,7 @@
         <v>0.67649999999999999</v>
       </c>
     </row>
-    <row r="342" spans="1:13" ht="43.5">
+    <row r="342" spans="1:13" ht="60">
       <c r="A342" s="1">
         <v>340</v>
       </c>
@@ -22788,7 +22788,7 @@
         <v>0.69840000000000002</v>
       </c>
     </row>
-    <row r="343" spans="1:13" ht="43.5">
+    <row r="343" spans="1:13" ht="60">
       <c r="A343" s="1">
         <v>341</v>
       </c>
@@ -22825,7 +22825,7 @@
         <v>0.75409999999999999</v>
       </c>
     </row>
-    <row r="344" spans="1:13" ht="43.5">
+    <row r="344" spans="1:13" ht="60">
       <c r="A344" s="1">
         <v>342</v>
       </c>
@@ -22862,7 +22862,7 @@
         <v>0.73529999999999995</v>
       </c>
     </row>
-    <row r="345" spans="1:13" ht="43.5">
+    <row r="345" spans="1:13" ht="45">
       <c r="A345" s="1">
         <v>343</v>
       </c>
@@ -22899,7 +22899,7 @@
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="346" spans="1:13" ht="43.5">
+    <row r="346" spans="1:13" ht="45">
       <c r="A346" s="1">
         <v>344</v>
       </c>
@@ -22936,7 +22936,7 @@
         <v>0.78690000000000004</v>
       </c>
     </row>
-    <row r="347" spans="1:13" ht="43.5">
+    <row r="347" spans="1:13" ht="60">
       <c r="A347" s="1">
         <v>345</v>
       </c>
@@ -22973,7 +22973,7 @@
         <v>0.64410000000000001</v>
       </c>
     </row>
-    <row r="348" spans="1:13" ht="29">
+    <row r="348" spans="1:13" ht="30">
       <c r="A348" s="1">
         <v>346</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="349" spans="1:13" ht="29">
+    <row r="349" spans="1:13" ht="30">
       <c r="A349" s="1">
         <v>347</v>
       </c>
@@ -23084,7 +23084,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="351" spans="1:13" ht="43.5">
+    <row r="351" spans="1:13" ht="45">
       <c r="A351" s="1">
         <v>349</v>
       </c>
@@ -23121,7 +23121,7 @@
         <v>0.26669999999999999</v>
       </c>
     </row>
-    <row r="352" spans="1:13" ht="43.5">
+    <row r="352" spans="1:13" ht="45">
       <c r="A352" s="1">
         <v>350</v>
       </c>
@@ -23158,7 +23158,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="353" spans="1:13" ht="43.5">
+    <row r="353" spans="1:13" ht="45">
       <c r="A353" s="1">
         <v>351</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>0.52629999999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:13" ht="43.5">
+    <row r="354" spans="1:13" ht="45">
       <c r="A354" s="1">
         <v>352</v>
       </c>
@@ -23232,7 +23232,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="355" spans="1:13" ht="43.5">
+    <row r="355" spans="1:13" ht="45">
       <c r="A355" s="1">
         <v>353</v>
       </c>
@@ -23269,7 +23269,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="356" spans="1:13" ht="43.5">
+    <row r="356" spans="1:13" ht="45">
       <c r="A356" s="1">
         <v>354</v>
       </c>
@@ -23306,7 +23306,7 @@
         <v>0.30769999999999997</v>
       </c>
     </row>
-    <row r="357" spans="1:13" ht="29">
+    <row r="357" spans="1:13" ht="30">
       <c r="A357" s="1">
         <v>355</v>
       </c>
@@ -23343,7 +23343,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="358" spans="1:13" ht="43.5">
+    <row r="358" spans="1:13" ht="45">
       <c r="A358" s="1">
         <v>356</v>
       </c>
@@ -23528,7 +23528,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="363" spans="1:13" ht="43.5">
+    <row r="363" spans="1:13" ht="45">
       <c r="A363" s="1">
         <v>361</v>
       </c>
@@ -23602,7 +23602,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="365" spans="1:13" ht="43.5">
+    <row r="365" spans="1:13" ht="45">
       <c r="A365" s="1">
         <v>363</v>
       </c>
@@ -23639,7 +23639,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="366" spans="1:13" ht="29">
+    <row r="366" spans="1:13" ht="45">
       <c r="A366" s="1">
         <v>364</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="367" spans="1:13" ht="29">
+    <row r="367" spans="1:13" ht="30">
       <c r="A367" s="1">
         <v>365</v>
       </c>
@@ -23787,7 +23787,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="370" spans="1:13" ht="29">
+    <row r="370" spans="1:13" ht="30">
       <c r="A370" s="1">
         <v>368</v>
       </c>
@@ -23824,7 +23824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="371" spans="1:13" ht="29">
+    <row r="371" spans="1:13" ht="30">
       <c r="A371" s="1">
         <v>369</v>
       </c>
@@ -23861,7 +23861,7 @@
         <v>0.70269999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:13" ht="29">
+    <row r="372" spans="1:13" ht="30">
       <c r="A372" s="1">
         <v>370</v>
       </c>
@@ -23935,7 +23935,7 @@
         <v>0.23530000000000001</v>
       </c>
     </row>
-    <row r="374" spans="1:13" ht="29">
+    <row r="374" spans="1:13" ht="30">
       <c r="A374" s="1">
         <v>372</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>0.3125</v>
       </c>
     </row>
-    <row r="375" spans="1:13" ht="29">
+    <row r="375" spans="1:13" ht="30">
       <c r="A375" s="1">
         <v>373</v>
       </c>
@@ -24009,7 +24009,7 @@
         <v>0.51280000000000003</v>
       </c>
     </row>
-    <row r="376" spans="1:13" ht="29">
+    <row r="376" spans="1:13" ht="30">
       <c r="A376" s="1">
         <v>374</v>
       </c>
@@ -24046,7 +24046,7 @@
         <v>0.41670000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:13" ht="29">
+    <row r="377" spans="1:13" ht="30">
       <c r="A377" s="1">
         <v>375</v>
       </c>
@@ -24083,7 +24083,7 @@
         <v>0.375</v>
       </c>
     </row>
-    <row r="378" spans="1:13" ht="29">
+    <row r="378" spans="1:13" ht="30">
       <c r="A378" s="1">
         <v>376</v>
       </c>
@@ -24120,7 +24120,7 @@
         <v>0.44440000000000002</v>
       </c>
     </row>
-    <row r="379" spans="1:13" ht="29">
+    <row r="379" spans="1:13" ht="30">
       <c r="A379" s="1">
         <v>377</v>
       </c>
@@ -24194,7 +24194,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="381" spans="1:13" ht="29">
+    <row r="381" spans="1:13" ht="30">
       <c r="A381" s="1">
         <v>379</v>
       </c>
@@ -24231,7 +24231,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="382" spans="1:13" ht="29">
+    <row r="382" spans="1:13" ht="30">
       <c r="A382" s="1">
         <v>380</v>
       </c>
@@ -24268,7 +24268,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="383" spans="1:13" ht="29">
+    <row r="383" spans="1:13" ht="30">
       <c r="A383" s="1">
         <v>381</v>
       </c>
@@ -24305,7 +24305,7 @@
         <v>0.7097</v>
       </c>
     </row>
-    <row r="384" spans="1:13" ht="29">
+    <row r="384" spans="1:13" ht="30">
       <c r="A384" s="1">
         <v>382</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="385" spans="1:13" ht="29">
+    <row r="385" spans="1:13" ht="30">
       <c r="A385" s="1">
         <v>383</v>
       </c>
@@ -24379,7 +24379,7 @@
         <v>0.76190000000000002</v>
       </c>
     </row>
-    <row r="386" spans="1:13" ht="29">
+    <row r="386" spans="1:13" ht="30">
       <c r="A386" s="1">
         <v>384</v>
       </c>
@@ -24416,7 +24416,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="387" spans="1:13" ht="29">
+    <row r="387" spans="1:13" ht="30">
       <c r="A387" s="1">
         <v>385</v>
       </c>
@@ -24453,7 +24453,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="388" spans="1:13" ht="29">
+    <row r="388" spans="1:13" ht="30">
       <c r="A388" s="1">
         <v>386</v>
       </c>
@@ -24490,7 +24490,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="389" spans="1:13">
+    <row r="389" spans="1:13" ht="30">
       <c r="A389" s="1">
         <v>387</v>
       </c>
@@ -24527,7 +24527,7 @@
         <v>0.52170000000000005</v>
       </c>
     </row>
-    <row r="390" spans="1:13" ht="29">
+    <row r="390" spans="1:13" ht="30">
       <c r="A390" s="1">
         <v>388</v>
       </c>
@@ -24675,7 +24675,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="394" spans="1:13" ht="29">
+    <row r="394" spans="1:13" ht="30">
       <c r="A394" s="1">
         <v>392</v>
       </c>
@@ -24749,7 +24749,7 @@
         <v>0.63160000000000005</v>
       </c>
     </row>
-    <row r="396" spans="1:13" ht="29">
+    <row r="396" spans="1:13" ht="30">
       <c r="A396" s="1">
         <v>394</v>
       </c>
@@ -24860,7 +24860,7 @@
         <v>0.71430000000000005</v>
       </c>
     </row>
-    <row r="399" spans="1:13" ht="29">
+    <row r="399" spans="1:13" ht="30">
       <c r="A399" s="1">
         <v>397</v>
       </c>
@@ -24934,7 +24934,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="401" spans="1:13" ht="29">
+    <row r="401" spans="1:13" ht="30">
       <c r="A401" s="1">
         <v>399</v>
       </c>
@@ -25008,7 +25008,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="403" spans="1:13" ht="29">
+    <row r="403" spans="1:13" ht="30">
       <c r="A403" s="1">
         <v>401</v>
       </c>
@@ -25045,7 +25045,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="404" spans="1:13" ht="29">
+    <row r="404" spans="1:13" ht="45">
       <c r="A404" s="1">
         <v>402</v>
       </c>
@@ -25082,7 +25082,7 @@
         <v>0.36359999999999998</v>
       </c>
     </row>
-    <row r="405" spans="1:13" ht="29">
+    <row r="405" spans="1:13" ht="30">
       <c r="A405" s="1">
         <v>403</v>
       </c>
@@ -25119,7 +25119,7 @@
         <v>0.3256</v>
       </c>
     </row>
-    <row r="406" spans="1:13" ht="29">
+    <row r="406" spans="1:13" ht="30">
       <c r="A406" s="1">
         <v>404</v>
       </c>
@@ -25156,7 +25156,7 @@
         <v>0.44440000000000002</v>
       </c>
     </row>
-    <row r="407" spans="1:13" ht="29">
+    <row r="407" spans="1:13" ht="30">
       <c r="A407" s="1">
         <v>405</v>
       </c>
@@ -25193,7 +25193,7 @@
         <v>0.44440000000000002</v>
       </c>
     </row>
-    <row r="408" spans="1:13" ht="29">
+    <row r="408" spans="1:13" ht="30">
       <c r="A408" s="1">
         <v>406</v>
       </c>
@@ -25230,7 +25230,7 @@
         <v>0.42109999999999997</v>
       </c>
     </row>
-    <row r="409" spans="1:13" ht="29">
+    <row r="409" spans="1:13" ht="30">
       <c r="A409" s="1">
         <v>407</v>
       </c>
@@ -25267,7 +25267,7 @@
         <v>0.28570000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:13" ht="29">
+    <row r="410" spans="1:13" ht="30">
       <c r="A410" s="1">
         <v>408</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="411" spans="1:13" ht="29">
+    <row r="411" spans="1:13" ht="30">
       <c r="A411" s="1">
         <v>409</v>
       </c>
@@ -25341,7 +25341,7 @@
         <v>0.70589999999999997</v>
       </c>
     </row>
-    <row r="412" spans="1:13" ht="29">
+    <row r="412" spans="1:13" ht="30">
       <c r="A412" s="1">
         <v>410</v>
       </c>
@@ -25378,7 +25378,7 @@
         <v>0.52939999999999998</v>
       </c>
     </row>
-    <row r="413" spans="1:13" ht="29">
+    <row r="413" spans="1:13" ht="30">
       <c r="A413" s="1">
         <v>411</v>
       </c>
@@ -25415,7 +25415,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="414" spans="1:13" ht="29">
+    <row r="414" spans="1:13" ht="30">
       <c r="A414" s="1">
         <v>412</v>
       </c>
@@ -25452,7 +25452,7 @@
         <v>0.28570000000000001</v>
       </c>
     </row>
-    <row r="415" spans="1:13" ht="29">
+    <row r="415" spans="1:13" ht="30">
       <c r="A415" s="1">
         <v>413</v>
       </c>
@@ -25489,7 +25489,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="416" spans="1:13" ht="29">
+    <row r="416" spans="1:13" ht="30">
       <c r="A416" s="1">
         <v>414</v>
       </c>
@@ -25526,7 +25526,7 @@
         <v>0.46150000000000002</v>
       </c>
     </row>
-    <row r="417" spans="1:13" ht="29">
+    <row r="417" spans="1:13" ht="30">
       <c r="A417" s="1">
         <v>415</v>
       </c>
@@ -25563,7 +25563,7 @@
         <v>0.36359999999999998</v>
       </c>
     </row>
-    <row r="418" spans="1:13" ht="29">
+    <row r="418" spans="1:13" ht="30">
       <c r="A418" s="1">
         <v>416</v>
       </c>
@@ -25600,7 +25600,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="419" spans="1:13" ht="29">
+    <row r="419" spans="1:13" ht="30">
       <c r="A419" s="1">
         <v>417</v>
       </c>
@@ -25637,7 +25637,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="420" spans="1:13" ht="29">
+    <row r="420" spans="1:13" ht="30">
       <c r="A420" s="1">
         <v>418</v>
       </c>
@@ -25674,7 +25674,7 @@
         <v>0.5333</v>
       </c>
     </row>
-    <row r="421" spans="1:13" ht="29">
+    <row r="421" spans="1:13" ht="30">
       <c r="A421" s="1">
         <v>419</v>
       </c>
@@ -25711,7 +25711,7 @@
         <v>0.28570000000000001</v>
       </c>
     </row>
-    <row r="422" spans="1:13" ht="29">
+    <row r="422" spans="1:13" ht="30">
       <c r="A422" s="1">
         <v>420</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="423" spans="1:13" ht="29">
+    <row r="423" spans="1:13" ht="30">
       <c r="A423" s="1">
         <v>421</v>
       </c>
@@ -25785,7 +25785,7 @@
         <v>0.35289999999999999</v>
       </c>
     </row>
-    <row r="424" spans="1:13" ht="29">
+    <row r="424" spans="1:13" ht="30">
       <c r="A424" s="1">
         <v>422</v>
       </c>
@@ -25822,7 +25822,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="425" spans="1:13" ht="43.5">
+    <row r="425" spans="1:13" ht="45">
       <c r="A425" s="1">
         <v>423</v>
       </c>
@@ -25859,7 +25859,7 @@
         <v>0.43480000000000002</v>
       </c>
     </row>
-    <row r="426" spans="1:13" ht="29">
+    <row r="426" spans="1:13" ht="30">
       <c r="A426" s="1">
         <v>424</v>
       </c>
@@ -25896,7 +25896,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="427" spans="1:13" ht="29">
+    <row r="427" spans="1:13" ht="30">
       <c r="A427" s="1">
         <v>425</v>
       </c>
@@ -25933,7 +25933,7 @@
         <v>0.51849999999999996</v>
       </c>
     </row>
-    <row r="428" spans="1:13" ht="29">
+    <row r="428" spans="1:13" ht="30">
       <c r="A428" s="1">
         <v>426</v>
       </c>
@@ -25970,7 +25970,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="429" spans="1:13" ht="29">
+    <row r="429" spans="1:13" ht="30">
       <c r="A429" s="1">
         <v>427</v>
       </c>
@@ -26007,7 +26007,7 @@
         <v>0.53849999999999998</v>
       </c>
     </row>
-    <row r="430" spans="1:13" ht="29">
+    <row r="430" spans="1:13" ht="30">
       <c r="A430" s="1">
         <v>428</v>
       </c>
@@ -26044,7 +26044,7 @@
         <v>0.51849999999999996</v>
       </c>
     </row>
-    <row r="431" spans="1:13" ht="43.5">
+    <row r="431" spans="1:13" ht="45">
       <c r="A431" s="1">
         <v>429</v>
       </c>
@@ -26081,7 +26081,7 @@
         <v>0.31819999999999998</v>
       </c>
     </row>
-    <row r="432" spans="1:13" ht="29">
+    <row r="432" spans="1:13" ht="30">
       <c r="A432" s="1">
         <v>430</v>
       </c>
@@ -26118,7 +26118,7 @@
         <v>0.86960000000000004</v>
       </c>
     </row>
-    <row r="433" spans="1:13" ht="29">
+    <row r="433" spans="1:13" ht="30">
       <c r="A433" s="1">
         <v>431</v>
       </c>
@@ -26155,7 +26155,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="434" spans="1:13" ht="29">
+    <row r="434" spans="1:13" ht="30">
       <c r="A434" s="1">
         <v>432</v>
       </c>
@@ -26192,7 +26192,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="435" spans="1:13" ht="43.5">
+    <row r="435" spans="1:13" ht="45">
       <c r="A435" s="1">
         <v>433</v>
       </c>
@@ -26229,7 +26229,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="436" spans="1:13" ht="29">
+    <row r="436" spans="1:13" ht="30">
       <c r="A436" s="1">
         <v>434</v>
       </c>
@@ -26266,7 +26266,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="437" spans="1:13" ht="29">
+    <row r="437" spans="1:13" ht="30">
       <c r="A437" s="1">
         <v>435</v>
       </c>
@@ -26340,7 +26340,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="439" spans="1:13" ht="29">
+    <row r="439" spans="1:13" ht="30">
       <c r="A439" s="1">
         <v>437</v>
       </c>
@@ -26377,7 +26377,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="440" spans="1:13" ht="29">
+    <row r="440" spans="1:13" ht="30">
       <c r="A440" s="1">
         <v>438</v>
       </c>
@@ -26414,7 +26414,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="441" spans="1:13" ht="29">
+    <row r="441" spans="1:13" ht="30">
       <c r="A441" s="1">
         <v>439</v>
       </c>
@@ -26451,7 +26451,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="442" spans="1:13" ht="29">
+    <row r="442" spans="1:13" ht="30">
       <c r="A442" s="1">
         <v>440</v>
       </c>
@@ -26488,7 +26488,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="443" spans="1:13" ht="29">
+    <row r="443" spans="1:13" ht="30">
       <c r="A443" s="1">
         <v>441</v>
       </c>
@@ -26525,7 +26525,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="444" spans="1:13" ht="29">
+    <row r="444" spans="1:13" ht="30">
       <c r="A444" s="1">
         <v>442</v>
       </c>
@@ -26562,7 +26562,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="445" spans="1:13" ht="29">
+    <row r="445" spans="1:13" ht="30">
       <c r="A445" s="1">
         <v>443</v>
       </c>
@@ -26599,7 +26599,7 @@
         <v>0.64859999999999995</v>
       </c>
     </row>
-    <row r="446" spans="1:13" ht="29">
+    <row r="446" spans="1:13" ht="30">
       <c r="A446" s="1">
         <v>444</v>
       </c>
@@ -26636,7 +26636,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="447" spans="1:13" ht="29">
+    <row r="447" spans="1:13" ht="30">
       <c r="A447" s="1">
         <v>445</v>
       </c>
@@ -26673,7 +26673,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="448" spans="1:13" ht="43.5">
+    <row r="448" spans="1:13" ht="45">
       <c r="A448" s="1">
         <v>446</v>
       </c>
@@ -26710,7 +26710,7 @@
         <v>0.52380000000000004</v>
       </c>
     </row>
-    <row r="449" spans="1:13" ht="29">
+    <row r="449" spans="1:13" ht="30">
       <c r="A449" s="1">
         <v>447</v>
       </c>
@@ -26747,7 +26747,7 @@
         <v>0.7097</v>
       </c>
     </row>
-    <row r="450" spans="1:13" ht="29">
+    <row r="450" spans="1:13" ht="30">
       <c r="A450" s="1">
         <v>448</v>
       </c>
@@ -26784,7 +26784,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="451" spans="1:13" ht="29">
+    <row r="451" spans="1:13" ht="30">
       <c r="A451" s="1">
         <v>449</v>
       </c>
@@ -26821,7 +26821,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="452" spans="1:13" ht="29">
+    <row r="452" spans="1:13" ht="30">
       <c r="A452" s="1">
         <v>450</v>
       </c>
@@ -26858,7 +26858,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="453" spans="1:13" ht="29">
+    <row r="453" spans="1:13" ht="30">
       <c r="A453" s="1">
         <v>451</v>
       </c>
@@ -26895,7 +26895,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="454" spans="1:13" ht="29">
+    <row r="454" spans="1:13" ht="30">
       <c r="A454" s="1">
         <v>452</v>
       </c>
@@ -26932,7 +26932,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="455" spans="1:13">
+    <row r="455" spans="1:13" ht="30">
       <c r="A455" s="1">
         <v>453</v>
       </c>
@@ -26969,7 +26969,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="456" spans="1:13" ht="29">
+    <row r="456" spans="1:13" ht="30">
       <c r="A456" s="1">
         <v>454</v>
       </c>
@@ -27006,7 +27006,7 @@
         <v>0.63639999999999997</v>
       </c>
     </row>
-    <row r="457" spans="1:13">
+    <row r="457" spans="1:13" ht="30">
       <c r="A457" s="1">
         <v>455</v>
       </c>
@@ -27043,7 +27043,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="458" spans="1:13" ht="29">
+    <row r="458" spans="1:13" ht="30">
       <c r="A458" s="1">
         <v>456</v>
       </c>
@@ -27080,7 +27080,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="459" spans="1:13" ht="29">
+    <row r="459" spans="1:13" ht="30">
       <c r="A459" s="1">
         <v>457</v>
       </c>
@@ -27117,7 +27117,7 @@
         <v>0.48280000000000001</v>
       </c>
     </row>
-    <row r="460" spans="1:13" ht="29">
+    <row r="460" spans="1:13" ht="30">
       <c r="A460" s="1">
         <v>458</v>
       </c>
@@ -27154,7 +27154,7 @@
         <v>0.3846</v>
       </c>
     </row>
-    <row r="461" spans="1:13" ht="29">
+    <row r="461" spans="1:13" ht="45">
       <c r="A461" s="1">
         <v>459</v>
       </c>
@@ -27191,7 +27191,7 @@
         <v>0.68289999999999995</v>
       </c>
     </row>
-    <row r="462" spans="1:13" ht="29">
+    <row r="462" spans="1:13" ht="30">
       <c r="A462" s="1">
         <v>460</v>
       </c>
@@ -27228,7 +27228,7 @@
         <v>0.2727</v>
       </c>
     </row>
-    <row r="463" spans="1:13">
+    <row r="463" spans="1:13" ht="30">
       <c r="A463" s="1">
         <v>461</v>
       </c>
@@ -27339,7 +27339,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="466" spans="1:13" ht="29">
+    <row r="466" spans="1:13" ht="30">
       <c r="A466" s="1">
         <v>464</v>
       </c>
@@ -27376,7 +27376,7 @@
         <v>0.28570000000000001</v>
       </c>
     </row>
-    <row r="467" spans="1:13" ht="29">
+    <row r="467" spans="1:13" ht="30">
       <c r="A467" s="1">
         <v>465</v>
       </c>
@@ -27413,7 +27413,7 @@
         <v>0.4375</v>
       </c>
     </row>
-    <row r="468" spans="1:13" ht="29">
+    <row r="468" spans="1:13" ht="30">
       <c r="A468" s="1">
         <v>466</v>
       </c>
@@ -27450,7 +27450,7 @@
         <v>0.60870000000000002</v>
       </c>
     </row>
-    <row r="469" spans="1:13" ht="29">
+    <row r="469" spans="1:13" ht="30">
       <c r="A469" s="1">
         <v>467</v>
       </c>
@@ -27487,7 +27487,7 @@
         <v>0.37840000000000001</v>
       </c>
     </row>
-    <row r="470" spans="1:13" ht="58">
+    <row r="470" spans="1:13" ht="60">
       <c r="A470" s="1">
         <v>468</v>
       </c>
@@ -27524,7 +27524,7 @@
         <v>0.35</v>
       </c>
     </row>
-    <row r="471" spans="1:13" ht="43.5">
+    <row r="471" spans="1:13" ht="45">
       <c r="A471" s="1">
         <v>469</v>
       </c>
@@ -27561,7 +27561,7 @@
         <v>0.42420000000000002</v>
       </c>
     </row>
-    <row r="472" spans="1:13" ht="43.5">
+    <row r="472" spans="1:13" ht="45">
       <c r="A472" s="1">
         <v>470</v>
       </c>
@@ -27598,7 +27598,7 @@
         <v>0.4118</v>
       </c>
     </row>
-    <row r="473" spans="1:13" ht="43.5">
+    <row r="473" spans="1:13" ht="45">
       <c r="A473" s="1">
         <v>471</v>
       </c>
@@ -27635,7 +27635,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="474" spans="1:13" ht="43.5">
+    <row r="474" spans="1:13" ht="45">
       <c r="A474" s="1">
         <v>472</v>
       </c>
@@ -27672,7 +27672,7 @@
         <v>0.73170000000000002</v>
       </c>
     </row>
-    <row r="475" spans="1:13">
+    <row r="475" spans="1:13" ht="30">
       <c r="A475" s="1">
         <v>473</v>
       </c>
@@ -27709,7 +27709,7 @@
         <v>0.91669999999999996</v>
       </c>
     </row>
-    <row r="476" spans="1:13" ht="43.5">
+    <row r="476" spans="1:13" ht="60">
       <c r="A476" s="1">
         <v>474</v>
       </c>
@@ -27746,7 +27746,7 @@
         <v>0.79310000000000003</v>
       </c>
     </row>
-    <row r="477" spans="1:13" ht="43.5">
+    <row r="477" spans="1:13" ht="45">
       <c r="A477" s="1">
         <v>475</v>
       </c>
@@ -27783,7 +27783,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="478" spans="1:13" ht="43.5">
+    <row r="478" spans="1:13" ht="45">
       <c r="A478" s="1">
         <v>476</v>
       </c>
@@ -27820,7 +27820,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="479" spans="1:13" ht="87">
+    <row r="479" spans="1:13" ht="90">
       <c r="A479" s="1">
         <v>477</v>
       </c>
@@ -27857,7 +27857,7 @@
         <v>0.7077</v>
       </c>
     </row>
-    <row r="480" spans="1:13" ht="58">
+    <row r="480" spans="1:13" ht="60">
       <c r="A480" s="1">
         <v>478</v>
       </c>
@@ -27894,7 +27894,7 @@
         <v>0.71430000000000005</v>
       </c>
     </row>
-    <row r="481" spans="1:13" ht="72.5">
+    <row r="481" spans="1:13" ht="75">
       <c r="A481" s="1">
         <v>479</v>
       </c>
@@ -27931,7 +27931,7 @@
         <v>0.72289999999999999</v>
       </c>
     </row>
-    <row r="482" spans="1:13" ht="29">
+    <row r="482" spans="1:13" ht="30">
       <c r="A482" s="1">
         <v>480</v>
       </c>
@@ -27968,7 +27968,7 @@
         <v>0.70269999999999999</v>
       </c>
     </row>
-    <row r="483" spans="1:13" ht="58">
+    <row r="483" spans="1:13" ht="60">
       <c r="A483" s="1">
         <v>481</v>
       </c>
@@ -28005,7 +28005,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="484" spans="1:13" ht="58">
+    <row r="484" spans="1:13" ht="60">
       <c r="A484" s="1">
         <v>482</v>
       </c>
@@ -28042,7 +28042,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="485" spans="1:13" ht="72.5">
+    <row r="485" spans="1:13" ht="75">
       <c r="A485" s="1">
         <v>483</v>
       </c>
@@ -28079,7 +28079,7 @@
         <v>0.7742</v>
       </c>
     </row>
-    <row r="486" spans="1:13" ht="58">
+    <row r="486" spans="1:13" ht="60">
       <c r="A486" s="1">
         <v>484</v>
       </c>
@@ -28116,7 +28116,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="487" spans="1:13" ht="72.5">
+    <row r="487" spans="1:13" ht="75">
       <c r="A487" s="1">
         <v>485</v>
       </c>
@@ -28153,7 +28153,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="488" spans="1:13" ht="72.5">
+    <row r="488" spans="1:13" ht="75">
       <c r="A488" s="1">
         <v>486</v>
       </c>
@@ -28190,7 +28190,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="489" spans="1:13" ht="29">
+    <row r="489" spans="1:13" ht="30">
       <c r="A489" s="1">
         <v>487</v>
       </c>
@@ -28227,7 +28227,7 @@
         <v>0.88</v>
       </c>
     </row>
-    <row r="490" spans="1:13" ht="29">
+    <row r="490" spans="1:13" ht="45">
       <c r="A490" s="1">
         <v>488</v>
       </c>
@@ -28264,7 +28264,7 @@
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="491" spans="1:13" ht="58">
+    <row r="491" spans="1:13" ht="60">
       <c r="A491" s="1">
         <v>489</v>
       </c>
@@ -28301,7 +28301,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="492" spans="1:13" ht="58">
+    <row r="492" spans="1:13" ht="60">
       <c r="A492" s="1">
         <v>490</v>
       </c>
@@ -28338,7 +28338,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="493" spans="1:13" ht="58">
+    <row r="493" spans="1:13" ht="60">
       <c r="A493" s="1">
         <v>491</v>
       </c>
@@ -28375,7 +28375,7 @@
         <v>0.69230000000000003</v>
       </c>
     </row>
-    <row r="494" spans="1:13" ht="29">
+    <row r="494" spans="1:13" ht="30">
       <c r="A494" s="1">
         <v>492</v>
       </c>
@@ -28412,7 +28412,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="495" spans="1:13" ht="58">
+    <row r="495" spans="1:13" ht="60">
       <c r="A495" s="1">
         <v>493</v>
       </c>
@@ -28449,7 +28449,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="496" spans="1:13" ht="58">
+    <row r="496" spans="1:13" ht="60">
       <c r="A496" s="1">
         <v>494</v>
       </c>
@@ -28486,7 +28486,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="497" spans="1:13" ht="29">
+    <row r="497" spans="1:13" ht="30">
       <c r="A497" s="1">
         <v>495</v>
       </c>
@@ -28523,7 +28523,7 @@
         <v>0.94740000000000002</v>
       </c>
     </row>
-    <row r="498" spans="1:13" ht="29">
+    <row r="498" spans="1:13" ht="30">
       <c r="A498" s="1">
         <v>496</v>
       </c>
@@ -28560,7 +28560,7 @@
         <v>0.94740000000000002</v>
       </c>
     </row>
-    <row r="499" spans="1:13" ht="29">
+    <row r="499" spans="1:13" ht="30">
       <c r="A499" s="1">
         <v>497</v>
       </c>
@@ -28597,7 +28597,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="500" spans="1:13" ht="29">
+    <row r="500" spans="1:13" ht="30">
       <c r="A500" s="1">
         <v>498</v>
       </c>
@@ -28634,7 +28634,7 @@
         <v>0.94740000000000002</v>
       </c>
     </row>
-    <row r="501" spans="1:13" ht="29">
+    <row r="501" spans="1:13" ht="30">
       <c r="A501" s="1">
         <v>499</v>
       </c>
@@ -28671,7 +28671,7 @@
         <v>0.94740000000000002</v>
       </c>
     </row>
-    <row r="502" spans="1:13" ht="29">
+    <row r="502" spans="1:13" ht="30">
       <c r="A502" s="1">
         <v>500</v>
       </c>
@@ -28708,7 +28708,7 @@
         <v>0.84209999999999996</v>
       </c>
     </row>
-    <row r="503" spans="1:13">
+    <row r="503" spans="1:13" ht="30">
       <c r="A503" s="1">
         <v>501</v>
       </c>
@@ -28745,7 +28745,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="504" spans="1:13" ht="43.5">
+    <row r="504" spans="1:13" ht="45">
       <c r="A504" s="1">
         <v>502</v>
       </c>
@@ -28782,7 +28782,7 @@
         <v>0.79310000000000003</v>
       </c>
     </row>
-    <row r="505" spans="1:13" ht="29">
+    <row r="505" spans="1:13" ht="30">
       <c r="A505" s="1">
         <v>503</v>
       </c>
@@ -28819,7 +28819,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="506" spans="1:13" ht="29">
+    <row r="506" spans="1:13" ht="30">
       <c r="A506" s="1">
         <v>504</v>
       </c>
@@ -28856,7 +28856,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="507" spans="1:13" ht="29">
+    <row r="507" spans="1:13" ht="30">
       <c r="A507" s="1">
         <v>505</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="508" spans="1:13" ht="29">
+    <row r="508" spans="1:13" ht="30">
       <c r="A508" s="1">
         <v>506</v>
       </c>
@@ -28930,7 +28930,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="509" spans="1:13" ht="29">
+    <row r="509" spans="1:13" ht="30">
       <c r="A509" s="1">
         <v>507</v>
       </c>
@@ -29004,7 +29004,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="511" spans="1:13" ht="29">
+    <row r="511" spans="1:13" ht="30">
       <c r="A511" s="1">
         <v>509</v>
       </c>
@@ -29078,7 +29078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="513" spans="1:13" ht="58">
+    <row r="513" spans="1:13" ht="60">
       <c r="A513" s="1">
         <v>511</v>
       </c>
@@ -29152,7 +29152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="515" spans="1:13" ht="29">
+    <row r="515" spans="1:13" ht="30">
       <c r="A515" s="1">
         <v>513</v>
       </c>
@@ -29189,7 +29189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="516" spans="1:13" ht="29">
+    <row r="516" spans="1:13" ht="30">
       <c r="A516" s="1">
         <v>514</v>
       </c>
@@ -29263,7 +29263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="518" spans="1:13" ht="29">
+    <row r="518" spans="1:13" ht="30">
       <c r="A518" s="1">
         <v>516</v>
       </c>
@@ -29300,7 +29300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="519" spans="1:13" ht="29">
+    <row r="519" spans="1:13" ht="30">
       <c r="A519" s="1">
         <v>517</v>
       </c>
@@ -29337,7 +29337,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="520" spans="1:13">
+    <row r="520" spans="1:13" ht="30">
       <c r="A520" s="1">
         <v>518</v>
       </c>
@@ -29448,7 +29448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="523" spans="1:13" ht="29">
+    <row r="523" spans="1:13" ht="30">
       <c r="A523" s="1">
         <v>521</v>
       </c>
@@ -29485,7 +29485,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="524" spans="1:13" ht="29">
+    <row r="524" spans="1:13" ht="30">
       <c r="A524" s="1">
         <v>522</v>
       </c>
@@ -29522,7 +29522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="525" spans="1:13">
+    <row r="525" spans="1:13" ht="30">
       <c r="A525" s="1">
         <v>523</v>
       </c>
@@ -29559,7 +29559,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="526" spans="1:13" ht="29">
+    <row r="526" spans="1:13" ht="30">
       <c r="A526" s="1">
         <v>524</v>
       </c>
@@ -29707,7 +29707,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="530" spans="1:13" ht="29">
+    <row r="530" spans="1:13" ht="30">
       <c r="A530" s="1">
         <v>528</v>
       </c>
@@ -29781,7 +29781,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="532" spans="1:13" ht="29">
+    <row r="532" spans="1:13" ht="30">
       <c r="A532" s="1">
         <v>530</v>
       </c>
@@ -29818,7 +29818,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="533" spans="1:13" ht="29">
+    <row r="533" spans="1:13" ht="30">
       <c r="A533" s="1">
         <v>531</v>
       </c>
@@ -29855,7 +29855,7 @@
         <v>0.84209999999999996</v>
       </c>
     </row>
-    <row r="534" spans="1:13" ht="29">
+    <row r="534" spans="1:13" ht="30">
       <c r="A534" s="1">
         <v>532</v>
       </c>
@@ -29929,7 +29929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="536" spans="1:13" ht="29">
+    <row r="536" spans="1:13" ht="30">
       <c r="A536" s="1">
         <v>534</v>
       </c>
@@ -29966,7 +29966,7 @@
         <v>0.92859999999999998</v>
       </c>
     </row>
-    <row r="537" spans="1:13" ht="29">
+    <row r="537" spans="1:13" ht="30">
       <c r="A537" s="1">
         <v>535</v>
       </c>
@@ -30003,7 +30003,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="538" spans="1:13" ht="29">
+    <row r="538" spans="1:13" ht="30">
       <c r="A538" s="1">
         <v>536</v>
       </c>
@@ -30040,7 +30040,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="539" spans="1:13" ht="43.5">
+    <row r="539" spans="1:13" ht="60">
       <c r="A539" s="1">
         <v>537</v>
       </c>
@@ -30077,7 +30077,7 @@
         <v>0.91890000000000005</v>
       </c>
     </row>
-    <row r="540" spans="1:13" ht="43.5">
+    <row r="540" spans="1:13" ht="45">
       <c r="A540" s="1">
         <v>538</v>
       </c>
@@ -30114,7 +30114,7 @@
         <v>0.96970000000000001</v>
       </c>
     </row>
-    <row r="541" spans="1:13" ht="29">
+    <row r="541" spans="1:13" ht="30">
       <c r="A541" s="1">
         <v>539</v>
       </c>
@@ -30151,7 +30151,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="542" spans="1:13" ht="43.5">
+    <row r="542" spans="1:13" ht="45">
       <c r="A542" s="1">
         <v>540</v>
       </c>
@@ -30188,7 +30188,7 @@
         <v>0.82609999999999995</v>
       </c>
     </row>
-    <row r="543" spans="1:13" ht="29">
+    <row r="543" spans="1:13" ht="30">
       <c r="A543" s="1">
         <v>541</v>
       </c>
@@ -30225,7 +30225,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="544" spans="1:13" ht="29">
+    <row r="544" spans="1:13" ht="30">
       <c r="A544" s="1">
         <v>542</v>
       </c>
@@ -30262,7 +30262,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="545" spans="1:13" ht="29">
+    <row r="545" spans="1:13" ht="30">
       <c r="A545" s="1">
         <v>543</v>
       </c>
@@ -30299,7 +30299,7 @@
         <v>0.875</v>
       </c>
     </row>
-    <row r="546" spans="1:13" ht="29">
+    <row r="546" spans="1:13" ht="30">
       <c r="A546" s="1">
         <v>544</v>
       </c>
@@ -30336,7 +30336,7 @@
         <v>0.9375</v>
       </c>
     </row>
-    <row r="547" spans="1:13" ht="29">
+    <row r="547" spans="1:13" ht="30">
       <c r="A547" s="1">
         <v>545</v>
       </c>
@@ -30373,7 +30373,7 @@
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="548" spans="1:13" ht="29">
+    <row r="548" spans="1:13" ht="30">
       <c r="A548" s="1">
         <v>546</v>
       </c>
@@ -30410,7 +30410,7 @@
         <v>0.88239999999999996</v>
       </c>
     </row>
-    <row r="549" spans="1:13" ht="29">
+    <row r="549" spans="1:13" ht="30">
       <c r="A549" s="1">
         <v>547</v>
       </c>
@@ -30447,7 +30447,7 @@
         <v>0.88239999999999996</v>
       </c>
     </row>
-    <row r="550" spans="1:13" ht="29">
+    <row r="550" spans="1:13" ht="30">
       <c r="A550" s="1">
         <v>548</v>
       </c>
@@ -30484,7 +30484,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="551" spans="1:13" ht="29">
+    <row r="551" spans="1:13" ht="30">
       <c r="A551" s="1">
         <v>549</v>
       </c>
@@ -30521,7 +30521,7 @@
         <v>0.88239999999999996</v>
       </c>
     </row>
-    <row r="552" spans="1:13" ht="29">
+    <row r="552" spans="1:13" ht="30">
       <c r="A552" s="1">
         <v>550</v>
       </c>
@@ -30706,7 +30706,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="557" spans="1:13" ht="29">
+    <row r="557" spans="1:13" ht="30">
       <c r="A557" s="1">
         <v>555</v>
       </c>
@@ -30743,7 +30743,7 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="558" spans="1:13" ht="29">
+    <row r="558" spans="1:13" ht="30">
       <c r="A558" s="1">
         <v>556</v>
       </c>
@@ -30780,7 +30780,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="559" spans="1:13" ht="29">
+    <row r="559" spans="1:13" ht="30">
       <c r="A559" s="1">
         <v>557</v>
       </c>
@@ -30817,7 +30817,7 @@
         <v>0.82050000000000001</v>
       </c>
     </row>
-    <row r="560" spans="1:13" ht="58">
+    <row r="560" spans="1:13" ht="75">
       <c r="A560" s="1">
         <v>558</v>
       </c>
@@ -30854,7 +30854,7 @@
         <v>0.90480000000000005</v>
       </c>
     </row>
-    <row r="561" spans="1:13" ht="29">
+    <row r="561" spans="1:13" ht="30">
       <c r="A561" s="1">
         <v>559</v>
       </c>
@@ -30891,7 +30891,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="562" spans="1:13" ht="43.5">
+    <row r="562" spans="1:13" ht="45">
       <c r="A562" s="1">
         <v>560</v>
       </c>
@@ -30965,7 +30965,7 @@
         <v>0.71430000000000005</v>
       </c>
     </row>
-    <row r="564" spans="1:13">
+    <row r="564" spans="1:13" ht="30">
       <c r="A564" s="1">
         <v>562</v>
       </c>
@@ -31002,7 +31002,7 @@
         <v>0.9143</v>
       </c>
     </row>
-    <row r="565" spans="1:13">
+    <row r="565" spans="1:13" ht="30">
       <c r="A565" s="1">
         <v>563</v>
       </c>
@@ -31446,7 +31446,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="577" spans="1:13" ht="29">
+    <row r="577" spans="1:13" ht="30">
       <c r="A577" s="1">
         <v>575</v>
       </c>
@@ -31483,7 +31483,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="578" spans="1:13" ht="29">
+    <row r="578" spans="1:13" ht="30">
       <c r="A578" s="1">
         <v>576</v>
       </c>
@@ -31557,7 +31557,7 @@
         <v>0.4118</v>
       </c>
     </row>
-    <row r="580" spans="1:13" ht="29">
+    <row r="580" spans="1:13" ht="30">
       <c r="A580" s="1">
         <v>578</v>
       </c>
@@ -31594,7 +31594,7 @@
         <v>0.72409999999999997</v>
       </c>
     </row>
-    <row r="581" spans="1:13" ht="29">
+    <row r="581" spans="1:13" ht="30">
       <c r="A581" s="1">
         <v>579</v>
       </c>
@@ -31631,7 +31631,7 @@
         <v>0.70589999999999997</v>
       </c>
     </row>
-    <row r="582" spans="1:13" ht="29">
+    <row r="582" spans="1:13" ht="30">
       <c r="A582" s="1">
         <v>580</v>
       </c>
@@ -31668,7 +31668,7 @@
         <v>0.51160000000000005</v>
       </c>
     </row>
-    <row r="583" spans="1:13" ht="29">
+    <row r="583" spans="1:13" ht="30">
       <c r="A583" s="1">
         <v>581</v>
       </c>
@@ -31705,7 +31705,7 @@
         <v>0.69769999999999999</v>
       </c>
     </row>
-    <row r="584" spans="1:13" ht="29">
+    <row r="584" spans="1:13" ht="30">
       <c r="A584" s="1">
         <v>582</v>
       </c>
@@ -31742,7 +31742,7 @@
         <v>0.59570000000000001</v>
       </c>
     </row>
-    <row r="585" spans="1:13" ht="29">
+    <row r="585" spans="1:13" ht="30">
       <c r="A585" s="1">
         <v>583</v>
       </c>
@@ -31853,7 +31853,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="588" spans="1:13" ht="29">
+    <row r="588" spans="1:13" ht="30">
       <c r="A588" s="1">
         <v>586</v>
       </c>
@@ -32112,7 +32112,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="595" spans="1:13" ht="29">
+    <row r="595" spans="1:13" ht="30">
       <c r="A595" s="1">
         <v>593</v>
       </c>
@@ -32149,7 +32149,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="596" spans="1:13" ht="29">
+    <row r="596" spans="1:13" ht="30">
       <c r="A596" s="1">
         <v>594</v>
       </c>
@@ -32186,7 +32186,7 @@
         <v>0.77549999999999997</v>
       </c>
     </row>
-    <row r="597" spans="1:13">
+    <row r="597" spans="1:13" ht="30">
       <c r="A597" s="1">
         <v>595</v>
       </c>
@@ -32260,7 +32260,7 @@
         <v>0.8125</v>
       </c>
     </row>
-    <row r="599" spans="1:13">
+    <row r="599" spans="1:13" ht="30">
       <c r="A599" s="1">
         <v>597</v>
       </c>
@@ -32297,7 +32297,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="600" spans="1:13" ht="29">
+    <row r="600" spans="1:13" ht="30">
       <c r="A600" s="1">
         <v>598</v>
       </c>
@@ -32334,7 +32334,7 @@
         <v>0.90480000000000005</v>
       </c>
     </row>
-    <row r="601" spans="1:13" ht="29">
+    <row r="601" spans="1:13" ht="30">
       <c r="A601" s="1">
         <v>599</v>
       </c>
@@ -32371,7 +32371,7 @@
         <v>0.88460000000000005</v>
       </c>
     </row>
-    <row r="602" spans="1:13" ht="43.5">
+    <row r="602" spans="1:13" ht="45">
       <c r="A602" s="1">
         <v>600</v>
       </c>
@@ -32445,7 +32445,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="604" spans="1:13" ht="29">
+    <row r="604" spans="1:13" ht="30">
       <c r="A604" s="1">
         <v>602</v>
       </c>
@@ -32556,7 +32556,7 @@
         <v>0.38100000000000001</v>
       </c>
     </row>
-    <row r="607" spans="1:13" ht="29">
+    <row r="607" spans="1:13" ht="30">
       <c r="A607" s="1">
         <v>605</v>
       </c>
@@ -32889,7 +32889,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="616" spans="1:13" ht="29">
+    <row r="616" spans="1:13" ht="30">
       <c r="A616" s="1">
         <v>614</v>
       </c>
@@ -33074,7 +33074,7 @@
         <v>0.61539999999999995</v>
       </c>
     </row>
-    <row r="621" spans="1:13" ht="29">
+    <row r="621" spans="1:13" ht="30">
       <c r="A621" s="1">
         <v>619</v>
       </c>
@@ -33296,7 +33296,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="627" spans="1:13">
+    <row r="627" spans="1:13" ht="30">
       <c r="A627" s="1">
         <v>625</v>
       </c>
@@ -33518,7 +33518,7 @@
         <v>0.96550000000000002</v>
       </c>
     </row>
-    <row r="633" spans="1:13" ht="29">
+    <row r="633" spans="1:13" ht="45">
       <c r="A633" s="1">
         <v>631</v>
       </c>
@@ -33629,7 +33629,7 @@
         <v>0.84850000000000003</v>
       </c>
     </row>
-    <row r="636" spans="1:13" ht="29">
+    <row r="636" spans="1:13" ht="45">
       <c r="A636" s="1">
         <v>634</v>
       </c>
@@ -33740,7 +33740,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="639" spans="1:13" ht="29">
+    <row r="639" spans="1:13" ht="30">
       <c r="A639" s="1">
         <v>637</v>
       </c>
@@ -34073,7 +34073,7 @@
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="648" spans="1:13" ht="29">
+    <row r="648" spans="1:13" ht="30">
       <c r="A648" s="1">
         <v>646</v>
       </c>
@@ -34110,7 +34110,7 @@
         <v>0.81079999999999997</v>
       </c>
     </row>
-    <row r="649" spans="1:13" ht="29">
+    <row r="649" spans="1:13" ht="30">
       <c r="A649" s="1">
         <v>647</v>
       </c>
@@ -34184,7 +34184,7 @@
         <v>0.51849999999999996</v>
       </c>
     </row>
-    <row r="651" spans="1:13" ht="29">
+    <row r="651" spans="1:13" ht="30">
       <c r="A651" s="1">
         <v>649</v>
       </c>
@@ -34258,7 +34258,7 @@
         <v>0.64</v>
       </c>
     </row>
-    <row r="653" spans="1:13">
+    <row r="653" spans="1:13" ht="30">
       <c r="A653" s="1">
         <v>651</v>
       </c>
@@ -34332,7 +34332,7 @@
         <v>0.78790000000000004</v>
       </c>
     </row>
-    <row r="655" spans="1:13" ht="29">
+    <row r="655" spans="1:13" ht="30">
       <c r="A655" s="1">
         <v>653</v>
       </c>
@@ -34369,7 +34369,7 @@
         <v>0.84440000000000004</v>
       </c>
     </row>
-    <row r="656" spans="1:13" ht="29">
+    <row r="656" spans="1:13" ht="30">
       <c r="A656" s="1">
         <v>654</v>
       </c>
@@ -34406,7 +34406,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="657" spans="1:13" ht="29">
+    <row r="657" spans="1:13" ht="30">
       <c r="A657" s="1">
         <v>655</v>
       </c>
@@ -34443,7 +34443,7 @@
         <v>0.54549999999999998</v>
       </c>
     </row>
-    <row r="658" spans="1:13" ht="29">
+    <row r="658" spans="1:13" ht="30">
       <c r="A658" s="1">
         <v>656</v>
       </c>
@@ -34480,7 +34480,7 @@
         <v>0.8095</v>
       </c>
     </row>
-    <row r="659" spans="1:13">
+    <row r="659" spans="1:13" ht="30">
       <c r="A659" s="1">
         <v>657</v>
       </c>
@@ -34517,7 +34517,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="660" spans="1:13">
+    <row r="660" spans="1:13" ht="30">
       <c r="A660" s="1">
         <v>658</v>
       </c>
@@ -34554,7 +34554,7 @@
         <v>0.73329999999999995</v>
       </c>
     </row>
-    <row r="661" spans="1:13" ht="29">
+    <row r="661" spans="1:13" ht="30">
       <c r="A661" s="1">
         <v>659</v>
       </c>
@@ -34665,7 +34665,7 @@
         <v>0.57140000000000002</v>
       </c>
     </row>
-    <row r="664" spans="1:13" ht="29">
+    <row r="664" spans="1:13" ht="30">
       <c r="A664" s="1">
         <v>662</v>
       </c>
@@ -34776,7 +34776,7 @@
         <v>0.60870000000000002</v>
       </c>
     </row>
-    <row r="667" spans="1:13">
+    <row r="667" spans="1:13" ht="30">
       <c r="A667" s="1">
         <v>665</v>
       </c>
@@ -34813,7 +34813,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="668" spans="1:13" ht="29">
+    <row r="668" spans="1:13" ht="45">
       <c r="A668" s="1">
         <v>666</v>
       </c>
@@ -34850,7 +34850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="669" spans="1:13" ht="29">
+    <row r="669" spans="1:13" ht="30">
       <c r="A669" s="1">
         <v>667</v>
       </c>
@@ -34887,7 +34887,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="670" spans="1:13" ht="29">
+    <row r="670" spans="1:13" ht="30">
       <c r="A670" s="1">
         <v>668</v>
       </c>
@@ -34924,7 +34924,7 @@
         <v>0.78049999999999997</v>
       </c>
     </row>
-    <row r="671" spans="1:13" ht="29">
+    <row r="671" spans="1:13" ht="30">
       <c r="A671" s="1">
         <v>669</v>
       </c>
@@ -34961,7 +34961,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="672" spans="1:13" ht="29">
+    <row r="672" spans="1:13" ht="30">
       <c r="A672" s="1">
         <v>670</v>
       </c>
@@ -35035,7 +35035,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="674" spans="1:13" ht="29">
+    <row r="674" spans="1:13" ht="30">
       <c r="A674" s="1">
         <v>672</v>
       </c>
@@ -35146,7 +35146,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="677" spans="1:13" ht="29">
+    <row r="677" spans="1:13" ht="30">
       <c r="A677" s="1">
         <v>675</v>
       </c>
@@ -35220,7 +35220,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="679" spans="1:13" ht="29">
+    <row r="679" spans="1:13" ht="30">
       <c r="A679" s="1">
         <v>677</v>
       </c>
@@ -35368,7 +35368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="683" spans="1:13" ht="29">
+    <row r="683" spans="1:13" ht="30">
       <c r="A683" s="1">
         <v>681</v>
       </c>
@@ -35479,7 +35479,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="686" spans="1:13" ht="29">
+    <row r="686" spans="1:13" ht="30">
       <c r="A686" s="1">
         <v>684</v>
       </c>
@@ -35516,7 +35516,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="687" spans="1:13">
+    <row r="687" spans="1:13" ht="30">
       <c r="A687" s="1">
         <v>685</v>
       </c>
@@ -35775,7 +35775,7 @@
         <v>0.88890000000000002</v>
       </c>
     </row>
-    <row r="694" spans="1:13" ht="43.5">
+    <row r="694" spans="1:13" ht="45">
       <c r="A694" s="1">
         <v>692</v>
       </c>
@@ -35849,7 +35849,7 @@
         <v>0.95650000000000002</v>
       </c>
     </row>
-    <row r="696" spans="1:13" ht="29">
+    <row r="696" spans="1:13" ht="30">
       <c r="A696" s="1">
         <v>694</v>
       </c>
@@ -36108,7 +36108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="703" spans="1:13" ht="29">
+    <row r="703" spans="1:13" ht="30">
       <c r="A703" s="1">
         <v>701</v>
       </c>
@@ -36182,7 +36182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="705" spans="1:13" ht="29">
+    <row r="705" spans="1:13" ht="30">
       <c r="A705" s="1">
         <v>703</v>
       </c>
@@ -36219,7 +36219,7 @@
         <v>0.93879999999999997</v>
       </c>
     </row>
-    <row r="706" spans="1:13" ht="29">
+    <row r="706" spans="1:13" ht="30">
       <c r="A706" s="1">
         <v>704</v>
       </c>
@@ -36256,7 +36256,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="707" spans="1:13" ht="29">
+    <row r="707" spans="1:13" ht="30">
       <c r="A707" s="1">
         <v>705</v>
       </c>
@@ -36293,7 +36293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="708" spans="1:13">
+    <row r="708" spans="1:13" ht="30">
       <c r="A708" s="1">
         <v>706</v>
       </c>
@@ -36330,7 +36330,7 @@
         <v>0.92310000000000003</v>
       </c>
     </row>
-    <row r="709" spans="1:13" ht="29">
+    <row r="709" spans="1:13" ht="30">
       <c r="A709" s="1">
         <v>707</v>
       </c>
@@ -36404,7 +36404,7 @@
         <v>0.97140000000000004</v>
       </c>
     </row>
-    <row r="711" spans="1:13" ht="29">
+    <row r="711" spans="1:13" ht="30">
       <c r="A711" s="1">
         <v>709</v>
       </c>
@@ -36441,7 +36441,7 @@
         <v>0.84209999999999996</v>
       </c>
     </row>
-    <row r="712" spans="1:13" ht="43.5">
+    <row r="712" spans="1:13" ht="45">
       <c r="A712" s="1">
         <v>710</v>
       </c>
@@ -36478,7 +36478,7 @@
         <v>0.85329999999999995</v>
       </c>
     </row>
-    <row r="713" spans="1:13" ht="29">
+    <row r="713" spans="1:13" ht="30">
       <c r="A713" s="1">
         <v>711</v>
       </c>
@@ -36700,7 +36700,7 @@
         <v>0.95240000000000002</v>
       </c>
     </row>
-    <row r="719" spans="1:13">
+    <row r="719" spans="1:13" ht="30">
       <c r="A719" s="1">
         <v>717</v>
       </c>
@@ -36774,7 +36774,7 @@
         <v>0.73680000000000001</v>
       </c>
     </row>
-    <row r="721" spans="1:13" ht="29">
+    <row r="721" spans="1:13" ht="30">
       <c r="A721" s="1">
         <v>719</v>
       </c>
@@ -37033,7 +37033,7 @@
         <v>0.94120000000000004</v>
       </c>
     </row>
-    <row r="728" spans="1:13" ht="29">
+    <row r="728" spans="1:13" ht="30">
       <c r="A728" s="1">
         <v>726</v>
       </c>
@@ -37070,7 +37070,7 @@
         <v>0.88460000000000005</v>
       </c>
     </row>
-    <row r="729" spans="1:13">
+    <row r="729" spans="1:13" ht="30">
       <c r="A729" s="1">
         <v>727</v>
       </c>
@@ -37107,7 +37107,7 @@
         <v>0.55559999999999998</v>
       </c>
     </row>
-    <row r="730" spans="1:13">
+    <row r="730" spans="1:13" ht="30">
       <c r="A730" s="1">
         <v>728</v>
       </c>
@@ -37181,7 +37181,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="732" spans="1:13" ht="29">
+    <row r="732" spans="1:13" ht="30">
       <c r="A732" s="1">
         <v>730</v>
       </c>
@@ -37218,7 +37218,7 @@
         <v>0.75860000000000005</v>
       </c>
     </row>
-    <row r="733" spans="1:13">
+    <row r="733" spans="1:13" ht="30">
       <c r="A733" s="1">
         <v>731</v>
       </c>
@@ -37255,7 +37255,7 @@
         <v>0.68969999999999998</v>
       </c>
     </row>
-    <row r="734" spans="1:13" ht="29">
+    <row r="734" spans="1:13" ht="30">
       <c r="A734" s="1">
         <v>732</v>
       </c>
@@ -37292,7 +37292,7 @@
         <v>0.76919999999999999</v>
       </c>
     </row>
-    <row r="735" spans="1:13">
+    <row r="735" spans="1:13" ht="30">
       <c r="A735" s="1">
         <v>733</v>
       </c>
@@ -37329,7 +37329,7 @@
         <v>0.77780000000000005</v>
       </c>
     </row>
-    <row r="736" spans="1:13" ht="29">
+    <row r="736" spans="1:13" ht="30">
       <c r="A736" s="1">
         <v>734</v>
       </c>
@@ -37403,7 +37403,7 @@
         <v>0.69569999999999999</v>
       </c>
     </row>
-    <row r="738" spans="1:13" ht="29">
+    <row r="738" spans="1:13" ht="30">
       <c r="A738" s="1">
         <v>736</v>
       </c>
@@ -37514,7 +37514,7 @@
         <v>0.78259999999999996</v>
       </c>
     </row>
-    <row r="741" spans="1:13" ht="29">
+    <row r="741" spans="1:13" ht="30">
       <c r="A741" s="1">
         <v>739</v>
       </c>
@@ -37551,7 +37551,7 @@
         <v>0.75560000000000005</v>
       </c>
     </row>
-    <row r="742" spans="1:13" ht="29">
+    <row r="742" spans="1:13" ht="30">
       <c r="A742" s="1">
         <v>740</v>
       </c>
@@ -37625,7 +37625,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="744" spans="1:13" ht="29">
+    <row r="744" spans="1:13" ht="30">
       <c r="A744" s="1">
         <v>742</v>
       </c>
@@ -37699,7 +37699,7 @@
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="746" spans="1:13">
+    <row r="746" spans="1:13" ht="30">
       <c r="A746" s="1">
         <v>744</v>
       </c>
@@ -37773,7 +37773,7 @@
         <v>0.76470000000000005</v>
       </c>
     </row>
-    <row r="748" spans="1:13" ht="29">
+    <row r="748" spans="1:13" ht="30">
       <c r="A748" s="1">
         <v>746</v>
       </c>
@@ -37810,7 +37810,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="749" spans="1:13" ht="29">
+    <row r="749" spans="1:13" ht="30">
       <c r="A749" s="1">
         <v>747</v>
       </c>
@@ -37847,7 +37847,7 @@
         <v>0.76600000000000001</v>
       </c>
     </row>
-    <row r="750" spans="1:13" ht="29">
+    <row r="750" spans="1:13" ht="30">
       <c r="A750" s="1">
         <v>748</v>
       </c>
@@ -37958,7 +37958,7 @@
         <v>0.7742</v>
       </c>
     </row>
-    <row r="753" spans="1:13" ht="29">
+    <row r="753" spans="1:13" ht="30">
       <c r="A753" s="1">
         <v>751</v>
       </c>
@@ -38032,7 +38032,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="755" spans="1:13">
+    <row r="755" spans="1:13" ht="30">
       <c r="A755" s="1">
         <v>753</v>
       </c>
@@ -38069,7 +38069,7 @@
         <v>0.76470000000000005</v>
       </c>
     </row>
-    <row r="756" spans="1:13" ht="29">
+    <row r="756" spans="1:13" ht="30">
       <c r="A756" s="1">
         <v>754</v>
       </c>
@@ -38106,7 +38106,7 @@
         <v>0.80649999999999999</v>
       </c>
     </row>
-    <row r="757" spans="1:13">
+    <row r="757" spans="1:13" ht="30">
       <c r="A757" s="1">
         <v>755</v>
       </c>
@@ -38143,7 +38143,7 @@
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="758" spans="1:13" ht="29">
+    <row r="758" spans="1:13" ht="30">
       <c r="A758" s="1">
         <v>756</v>
       </c>
@@ -38180,7 +38180,7 @@
         <v>0.90569999999999995</v>
       </c>
     </row>
-    <row r="759" spans="1:13" ht="29">
+    <row r="759" spans="1:13" ht="30">
       <c r="A759" s="1">
         <v>757</v>
       </c>
@@ -38365,7 +38365,7 @@
         <v>0.66669999999999996</v>
       </c>
     </row>
-    <row r="764" spans="1:13" ht="29">
+    <row r="764" spans="1:13" ht="30">
       <c r="A764" s="1">
         <v>762</v>
       </c>
@@ -38439,7 +38439,7 @@
         <v>0.72729999999999995</v>
       </c>
     </row>
-    <row r="766" spans="1:13" ht="29">
+    <row r="766" spans="1:13" ht="30">
       <c r="A766" s="1">
         <v>764</v>
       </c>
@@ -38476,7 +38476,7 @@
         <v>0.63329999999999997</v>
       </c>
     </row>
-    <row r="767" spans="1:13" ht="29">
+    <row r="767" spans="1:13" ht="30">
       <c r="A767" s="1">
         <v>765</v>
       </c>
@@ -38513,7 +38513,7 @@
         <v>0.8649</v>
       </c>
     </row>
-    <row r="768" spans="1:13" ht="29">
+    <row r="768" spans="1:13" ht="30">
       <c r="A768" s="1">
         <v>766</v>
       </c>
@@ -38550,7 +38550,7 @@
         <v>0.84850000000000003</v>
       </c>
     </row>
-    <row r="769" spans="1:13" ht="29">
+    <row r="769" spans="1:13" ht="30">
       <c r="A769" s="1">
         <v>767</v>
       </c>
@@ -38587,7 +38587,7 @@
         <v>0.83330000000000004</v>
       </c>
     </row>
-    <row r="770" spans="1:13" ht="29">
+    <row r="770" spans="1:13" ht="45">
       <c r="A770" s="1">
         <v>768</v>
       </c>
@@ -38624,7 +38624,7 @@
         <v>0.871</v>
       </c>
     </row>
-    <row r="771" spans="1:13" ht="29">
+    <row r="771" spans="1:13" ht="30">
       <c r="A771" s="1">
         <v>769</v>
       </c>
@@ -39105,7 +39105,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="784" spans="1:13" ht="29">
+    <row r="784" spans="1:13" ht="30">
       <c r="A784" s="1">
         <v>782</v>
       </c>
@@ -39142,7 +39142,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="785" spans="1:13" ht="29">
+    <row r="785" spans="1:13" ht="30">
       <c r="A785" s="1">
         <v>783</v>
       </c>
@@ -39179,7 +39179,7 @@
         <v>0.85</v>
       </c>
     </row>
-    <row r="786" spans="1:13" ht="29">
+    <row r="786" spans="1:13" ht="30">
       <c r="A786" s="1">
         <v>784</v>
       </c>
@@ -39216,7 +39216,7 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="787" spans="1:13" ht="29">
+    <row r="787" spans="1:13" ht="30">
       <c r="A787" s="1">
         <v>785</v>
       </c>
@@ -39253,7 +39253,7 @@
         <v>0.87270000000000003</v>
       </c>
     </row>
-    <row r="788" spans="1:13" ht="29">
+    <row r="788" spans="1:13" ht="30">
       <c r="A788" s="1">
         <v>786</v>
       </c>
@@ -39290,7 +39290,7 @@
         <v>0.82930000000000004</v>
       </c>
     </row>
-    <row r="789" spans="1:13" ht="29">
+    <row r="789" spans="1:13" ht="30">
       <c r="A789" s="1">
         <v>787</v>
       </c>
@@ -39401,7 +39401,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="792" spans="1:13" ht="29">
+    <row r="792" spans="1:13" ht="30">
       <c r="A792" s="1">
         <v>790</v>
       </c>
@@ -39438,7 +39438,7 @@
         <v>0.84209999999999996</v>
       </c>
     </row>
-    <row r="793" spans="1:13" ht="29">
+    <row r="793" spans="1:13" ht="30">
       <c r="A793" s="1">
         <v>791</v>
       </c>
@@ -39512,7 +39512,7 @@
         <v>0.85709999999999997</v>
       </c>
     </row>
-    <row r="795" spans="1:13">
+    <row r="795" spans="1:13" ht="30">
       <c r="A795" s="1">
         <v>793</v>
       </c>
@@ -39586,7 +39586,7 @@
         <v>0.84619999999999995</v>
       </c>
     </row>
-    <row r="797" spans="1:13" ht="29">
+    <row r="797" spans="1:13" ht="30">
       <c r="A797" s="1">
         <v>795</v>
       </c>
@@ -39623,7 +39623,7 @@
         <v>0.8387</v>
       </c>
     </row>
-    <row r="798" spans="1:13" ht="29">
+    <row r="798" spans="1:13" ht="30">
       <c r="A798" s="1">
         <v>796</v>
       </c>
@@ -39697,7 +39697,7 @@
         <v>0.81479999999999997</v>
       </c>
     </row>
-    <row r="800" spans="1:13" ht="29">
+    <row r="800" spans="1:13" ht="30">
       <c r="A800" s="1">
         <v>798</v>
       </c>
@@ -39734,7 +39734,7 @@
         <v>0.80769999999999997</v>
       </c>
     </row>
-    <row r="801" spans="1:13">
+    <row r="801" spans="1:13" ht="30">
       <c r="A801" s="1">
         <v>799</v>
       </c>
@@ -39771,7 +39771,7 @@
         <v>0.81079999999999997</v>
       </c>
     </row>
-    <row r="802" spans="1:13" ht="29">
+    <row r="802" spans="1:13" ht="30">
       <c r="A802" s="1">
         <v>800</v>
       </c>
@@ -39808,7 +39808,7 @@
         <v>0.878</v>
       </c>
     </row>
-    <row r="803" spans="1:13" ht="29">
+    <row r="803" spans="1:13" ht="30">
       <c r="A803" s="1">
         <v>801</v>
       </c>
@@ -39845,7 +39845,7 @@
         <v>0.81820000000000004</v>
       </c>
     </row>
-    <row r="804" spans="1:13" ht="29">
+    <row r="804" spans="1:13" ht="30">
       <c r="A804" s="1">
         <v>802</v>
       </c>
@@ -39882,7 +39882,7 @@
         <v>0.75560000000000005</v>
       </c>
     </row>
-    <row r="805" spans="1:13" ht="29">
+    <row r="805" spans="1:13" ht="30">
       <c r="A805" s="1">
         <v>803</v>
       </c>
@@ -40124,14 +40124,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE8B6B40-36A4-46E0-B5BF-0E3E172AEB25}">
   <dimension ref="A1:F1121"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.54296875" customWidth="1"/>
-    <col min="3" max="3" width="62.1796875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5703125" customWidth="1"/>
+    <col min="3" max="3" width="62.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="79" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.54296875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.5703125" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
@@ -40154,7 +40154,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29">
+    <row r="2" spans="1:6" ht="30">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -40174,7 +40174,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="29">
+    <row r="3" spans="1:6" ht="30">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -40194,7 +40194,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="29">
+    <row r="4" spans="1:6" ht="30">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -40214,7 +40214,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29">
+    <row r="5" spans="1:6" ht="30">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -40232,7 +40232,7 @@
       </c>
       <c r="F5" s="12"/>
     </row>
-    <row r="6" spans="1:6" ht="29">
+    <row r="6" spans="1:6" ht="30">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -40250,7 +40250,7 @@
       </c>
       <c r="F6" s="12"/>
     </row>
-    <row r="7" spans="1:6" ht="29">
+    <row r="7" spans="1:6" ht="30">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -40268,7 +40268,7 @@
       </c>
       <c r="F7" s="12"/>
     </row>
-    <row r="8" spans="1:6" ht="58">
+    <row r="8" spans="1:6" ht="60">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -40286,7 +40286,7 @@
       </c>
       <c r="F8" s="12"/>
     </row>
-    <row r="9" spans="1:6" ht="29">
+    <row r="9" spans="1:6" ht="30">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -40304,7 +40304,7 @@
       </c>
       <c r="F9" s="12"/>
     </row>
-    <row r="10" spans="1:6" ht="29">
+    <row r="10" spans="1:6" ht="30">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -40322,7 +40322,7 @@
       </c>
       <c r="F10" s="12"/>
     </row>
-    <row r="11" spans="1:6" ht="29">
+    <row r="11" spans="1:6" ht="30">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -40340,7 +40340,7 @@
       </c>
       <c r="F11" s="12"/>
     </row>
-    <row r="12" spans="1:6" ht="14.5" customHeight="1">
+    <row r="12" spans="1:6" ht="14.45" customHeight="1">
       <c r="A12" s="1">
         <v>12</v>
       </c>
@@ -40358,7 +40358,7 @@
       </c>
       <c r="F12" s="12"/>
     </row>
-    <row r="13" spans="1:6" ht="14.5" customHeight="1">
+    <row r="13" spans="1:6" ht="14.45" customHeight="1">
       <c r="A13" s="1">
         <v>13</v>
       </c>
@@ -40376,7 +40376,7 @@
       </c>
       <c r="F13" s="12"/>
     </row>
-    <row r="14" spans="1:6" ht="14.5" customHeight="1">
+    <row r="14" spans="1:6" ht="14.45" customHeight="1">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -40394,7 +40394,7 @@
       </c>
       <c r="F14" s="12"/>
     </row>
-    <row r="15" spans="1:6" ht="14.5" customHeight="1">
+    <row r="15" spans="1:6" ht="14.45" customHeight="1">
       <c r="A15" s="1">
         <v>15</v>
       </c>
@@ -40412,7 +40412,7 @@
       </c>
       <c r="F15" s="12"/>
     </row>
-    <row r="16" spans="1:6" ht="29">
+    <row r="16" spans="1:6" ht="30">
       <c r="A16" s="1">
         <v>16</v>
       </c>
@@ -40430,7 +40430,7 @@
       </c>
       <c r="F16" s="12"/>
     </row>
-    <row r="17" spans="1:6" ht="14.5" customHeight="1">
+    <row r="17" spans="1:6" ht="14.45" customHeight="1">
       <c r="A17" s="1">
         <v>17</v>
       </c>
@@ -40484,7 +40484,7 @@
       </c>
       <c r="F19" s="12"/>
     </row>
-    <row r="20" spans="1:6" ht="14.5" customHeight="1">
+    <row r="20" spans="1:6" ht="14.45" customHeight="1">
       <c r="A20" s="1">
         <v>20</v>
       </c>
@@ -40502,7 +40502,7 @@
       </c>
       <c r="F20" s="12"/>
     </row>
-    <row r="21" spans="1:6" ht="28">
+    <row r="21" spans="1:6" ht="28.5">
       <c r="A21" s="1">
         <v>21</v>
       </c>
@@ -40520,7 +40520,7 @@
       </c>
       <c r="F21" s="12"/>
     </row>
-    <row r="22" spans="1:6" ht="72.5">
+    <row r="22" spans="1:6" ht="75">
       <c r="A22" s="1">
         <v>22</v>
       </c>
@@ -40538,7 +40538,7 @@
       </c>
       <c r="F22" s="12"/>
     </row>
-    <row r="23" spans="1:6" ht="28">
+    <row r="23" spans="1:6" ht="30">
       <c r="A23" s="1">
         <v>23</v>
       </c>
@@ -40556,7 +40556,7 @@
       </c>
       <c r="F23" s="12"/>
     </row>
-    <row r="24" spans="1:6" ht="43.5">
+    <row r="24" spans="1:6" ht="60">
       <c r="A24" s="1">
         <v>25</v>
       </c>
@@ -40610,7 +40610,7 @@
       </c>
       <c r="F26" s="12"/>
     </row>
-    <row r="27" spans="1:6" ht="72.5">
+    <row r="27" spans="1:6" ht="90">
       <c r="A27" s="1">
         <v>28</v>
       </c>
@@ -40646,7 +40646,7 @@
       </c>
       <c r="F28" s="12"/>
     </row>
-    <row r="29" spans="1:6" ht="43.5">
+    <row r="29" spans="1:6" ht="45">
       <c r="A29" s="1">
         <v>30</v>
       </c>
@@ -40664,7 +40664,7 @@
       </c>
       <c r="F29" s="12"/>
     </row>
-    <row r="30" spans="1:6" ht="14.5" customHeight="1">
+    <row r="30" spans="1:6" ht="14.45" customHeight="1">
       <c r="A30" s="1">
         <v>31</v>
       </c>
@@ -40682,7 +40682,7 @@
       </c>
       <c r="F30" s="12"/>
     </row>
-    <row r="31" spans="1:6" ht="14.5" customHeight="1">
+    <row r="31" spans="1:6" ht="14.45" customHeight="1">
       <c r="A31" s="1">
         <v>32</v>
       </c>
@@ -40754,7 +40754,7 @@
       </c>
       <c r="F34" s="12"/>
     </row>
-    <row r="35" spans="1:6" ht="116">
+    <row r="35" spans="1:6" ht="120">
       <c r="A35" s="1">
         <v>39</v>
       </c>
@@ -40772,7 +40772,7 @@
       </c>
       <c r="F35" s="12"/>
     </row>
-    <row r="36" spans="1:6" ht="29">
+    <row r="36" spans="1:6" ht="30">
       <c r="A36" s="1">
         <v>40</v>
       </c>
@@ -40790,7 +40790,7 @@
       </c>
       <c r="F36" s="12"/>
     </row>
-    <row r="37" spans="1:6" ht="29">
+    <row r="37" spans="1:6" ht="30">
       <c r="A37" s="1">
         <v>41</v>
       </c>
@@ -40808,7 +40808,7 @@
       </c>
       <c r="F37" s="12"/>
     </row>
-    <row r="38" spans="1:6" ht="14.5" customHeight="1">
+    <row r="38" spans="1:6" ht="14.45" customHeight="1">
       <c r="A38" s="1">
         <v>42</v>
       </c>
@@ -40844,7 +40844,7 @@
       </c>
       <c r="F39" s="12"/>
     </row>
-    <row r="40" spans="1:6" ht="29">
+    <row r="40" spans="1:6" ht="30">
       <c r="A40" s="1">
         <v>44</v>
       </c>
@@ -40878,7 +40878,7 @@
       </c>
       <c r="F41" s="12"/>
     </row>
-    <row r="42" spans="1:6" ht="43.5">
+    <row r="42" spans="1:6" ht="60">
       <c r="A42" s="1">
         <v>46</v>
       </c>
@@ -40896,7 +40896,7 @@
       </c>
       <c r="F42" s="12"/>
     </row>
-    <row r="43" spans="1:6" ht="14.5" customHeight="1">
+    <row r="43" spans="1:6" ht="14.45" customHeight="1">
       <c r="A43" s="1">
         <v>48</v>
       </c>
@@ -40914,7 +40914,7 @@
       </c>
       <c r="F43" s="12"/>
     </row>
-    <row r="44" spans="1:6" ht="29">
+    <row r="44" spans="1:6" ht="30">
       <c r="A44" s="1">
         <v>50</v>
       </c>
@@ -40932,7 +40932,7 @@
       </c>
       <c r="F44" s="12"/>
     </row>
-    <row r="45" spans="1:6" ht="14.5" customHeight="1">
+    <row r="45" spans="1:6" ht="14.45" customHeight="1">
       <c r="A45" s="1">
         <v>51</v>
       </c>
@@ -40968,7 +40968,7 @@
       </c>
       <c r="F46" s="12"/>
     </row>
-    <row r="47" spans="1:6" ht="14.5" customHeight="1">
+    <row r="47" spans="1:6" ht="14.45" customHeight="1">
       <c r="A47" s="1">
         <v>53</v>
       </c>
@@ -40986,7 +40986,7 @@
       </c>
       <c r="F47" s="12"/>
     </row>
-    <row r="48" spans="1:6" ht="87">
+    <row r="48" spans="1:6" ht="90">
       <c r="A48" s="1">
         <v>54</v>
       </c>
@@ -41004,7 +41004,7 @@
       </c>
       <c r="F48" s="12"/>
     </row>
-    <row r="49" spans="1:6" ht="29">
+    <row r="49" spans="1:6" ht="45">
       <c r="A49" s="1">
         <v>55</v>
       </c>
@@ -41022,7 +41022,7 @@
       </c>
       <c r="F49" s="12"/>
     </row>
-    <row r="50" spans="1:6" ht="14.5" customHeight="1">
+    <row r="50" spans="1:6" ht="14.45" customHeight="1">
       <c r="A50" s="1">
         <v>56</v>
       </c>
@@ -41040,7 +41040,7 @@
       </c>
       <c r="F50" s="12"/>
     </row>
-    <row r="51" spans="1:6" ht="14.5" customHeight="1">
+    <row r="51" spans="1:6" ht="14.45" customHeight="1">
       <c r="A51" s="1">
         <v>57</v>
       </c>
@@ -41058,7 +41058,7 @@
       </c>
       <c r="F51" s="12"/>
     </row>
-    <row r="52" spans="1:6" ht="14.5" customHeight="1">
+    <row r="52" spans="1:6" ht="14.45" customHeight="1">
       <c r="A52" s="1">
         <v>58</v>
       </c>
@@ -41094,7 +41094,7 @@
       </c>
       <c r="F53" s="12"/>
     </row>
-    <row r="54" spans="1:6" ht="14.5" customHeight="1">
+    <row r="54" spans="1:6" ht="14.45" customHeight="1">
       <c r="A54" s="1">
         <v>60</v>
       </c>
@@ -41112,7 +41112,7 @@
       </c>
       <c r="F54" s="12"/>
     </row>
-    <row r="55" spans="1:6" ht="14.5" customHeight="1">
+    <row r="55" spans="1:6" ht="14.45" customHeight="1">
       <c r="A55" s="1">
         <v>61</v>
       </c>
@@ -41148,7 +41148,7 @@
       </c>
       <c r="F56" s="12"/>
     </row>
-    <row r="57" spans="1:6" ht="14.5" customHeight="1">
+    <row r="57" spans="1:6" ht="14.45" customHeight="1">
       <c r="A57" s="1">
         <v>63</v>
       </c>
@@ -41234,7 +41234,7 @@
       </c>
       <c r="F61" s="12"/>
     </row>
-    <row r="62" spans="1:6" ht="43.5">
+    <row r="62" spans="1:6" ht="45">
       <c r="A62" s="1">
         <v>70</v>
       </c>
@@ -41252,7 +41252,7 @@
       </c>
       <c r="F62" s="12"/>
     </row>
-    <row r="63" spans="1:6" ht="14.5" customHeight="1">
+    <row r="63" spans="1:6" ht="14.45" customHeight="1">
       <c r="A63" s="1">
         <v>71</v>
       </c>
@@ -41270,7 +41270,7 @@
       </c>
       <c r="F63" s="12"/>
     </row>
-    <row r="64" spans="1:6" ht="14.5" customHeight="1">
+    <row r="64" spans="1:6" ht="14.45" customHeight="1">
       <c r="A64" s="1">
         <v>72</v>
       </c>
@@ -41288,7 +41288,7 @@
       </c>
       <c r="F64" s="12"/>
     </row>
-    <row r="65" spans="1:6" ht="29">
+    <row r="65" spans="1:6" ht="30">
       <c r="A65" s="1">
         <v>73</v>
       </c>
@@ -41306,7 +41306,7 @@
       </c>
       <c r="F65" s="12"/>
     </row>
-    <row r="66" spans="1:6" ht="14.5" customHeight="1">
+    <row r="66" spans="1:6" ht="14.45" customHeight="1">
       <c r="A66" s="1">
         <v>74</v>
       </c>
@@ -41324,7 +41324,7 @@
       </c>
       <c r="F66" s="12"/>
     </row>
-    <row r="67" spans="1:6" ht="29">
+    <row r="67" spans="1:6" ht="30">
       <c r="A67" s="1">
         <v>75</v>
       </c>
@@ -41342,7 +41342,7 @@
       </c>
       <c r="F67" s="12"/>
     </row>
-    <row r="68" spans="1:6" ht="14.5" customHeight="1">
+    <row r="68" spans="1:6" ht="14.45" customHeight="1">
       <c r="A68" s="1">
         <v>76</v>
       </c>
@@ -41360,7 +41360,7 @@
       </c>
       <c r="F68" s="12"/>
     </row>
-    <row r="69" spans="1:6" ht="14.5" customHeight="1">
+    <row r="69" spans="1:6" ht="14.45" customHeight="1">
       <c r="A69" s="1">
         <v>77</v>
       </c>
@@ -41378,7 +41378,7 @@
       </c>
       <c r="F69" s="12"/>
     </row>
-    <row r="70" spans="1:6" ht="14.5" customHeight="1">
+    <row r="70" spans="1:6" ht="14.45" customHeight="1">
       <c r="A70" s="1">
         <v>78</v>
       </c>
@@ -41396,7 +41396,7 @@
       </c>
       <c r="F70" s="12"/>
     </row>
-    <row r="71" spans="1:6" ht="29.15" customHeight="1">
+    <row r="71" spans="1:6" ht="29.1" customHeight="1">
       <c r="A71" s="1">
         <v>79</v>
       </c>
@@ -41414,7 +41414,7 @@
       </c>
       <c r="F71" s="12"/>
     </row>
-    <row r="72" spans="1:6" ht="116">
+    <row r="72" spans="1:6" ht="135">
       <c r="A72" s="1">
         <v>80</v>
       </c>
@@ -41432,7 +41432,7 @@
       </c>
       <c r="F72" s="12"/>
     </row>
-    <row r="73" spans="1:6" ht="14.5" customHeight="1">
+    <row r="73" spans="1:6" ht="14.45" customHeight="1">
       <c r="A73" s="1">
         <v>81</v>
       </c>
@@ -41450,7 +41450,7 @@
       </c>
       <c r="F73" s="12"/>
     </row>
-    <row r="74" spans="1:6" ht="14.5" customHeight="1">
+    <row r="74" spans="1:6" ht="14.45" customHeight="1">
       <c r="A74" s="1">
         <v>82</v>
       </c>
@@ -41468,7 +41468,7 @@
       </c>
       <c r="F74" s="12"/>
     </row>
-    <row r="75" spans="1:6" ht="14.5" customHeight="1">
+    <row r="75" spans="1:6" ht="14.45" customHeight="1">
       <c r="A75" s="1">
         <v>85</v>
       </c>
@@ -41486,7 +41486,7 @@
       </c>
       <c r="F75" s="12"/>
     </row>
-    <row r="76" spans="1:6" ht="29">
+    <row r="76" spans="1:6" ht="30">
       <c r="A76" s="1">
         <v>86</v>
       </c>
@@ -41504,7 +41504,7 @@
       </c>
       <c r="F76" s="12"/>
     </row>
-    <row r="77" spans="1:6" ht="14.5" customHeight="1">
+    <row r="77" spans="1:6" ht="14.45" customHeight="1">
       <c r="A77" s="1">
         <v>87</v>
       </c>
@@ -41522,7 +41522,7 @@
       </c>
       <c r="F77" s="12"/>
     </row>
-    <row r="78" spans="1:6" ht="14.5" customHeight="1">
+    <row r="78" spans="1:6" ht="14.45" customHeight="1">
       <c r="A78" s="1">
         <v>88</v>
       </c>
@@ -41540,7 +41540,7 @@
       </c>
       <c r="F78" s="12"/>
     </row>
-    <row r="79" spans="1:6" ht="14.5" customHeight="1">
+    <row r="79" spans="1:6" ht="14.45" customHeight="1">
       <c r="A79" s="1">
         <v>89</v>
       </c>
@@ -41558,7 +41558,7 @@
       </c>
       <c r="F79" s="12"/>
     </row>
-    <row r="80" spans="1:6" ht="14.5" customHeight="1">
+    <row r="80" spans="1:6" ht="14.45" customHeight="1">
       <c r="A80" s="1">
         <v>90</v>
       </c>
@@ -41576,7 +41576,7 @@
       </c>
       <c r="F80" s="12"/>
     </row>
-    <row r="81" spans="1:6" ht="14.5" customHeight="1">
+    <row r="81" spans="1:6" ht="14.45" customHeight="1">
       <c r="A81" s="1">
         <v>92</v>
       </c>
@@ -41594,7 +41594,7 @@
       </c>
       <c r="F81" s="12"/>
     </row>
-    <row r="82" spans="1:6" ht="14.5" customHeight="1">
+    <row r="82" spans="1:6" ht="14.45" customHeight="1">
       <c r="A82" s="1">
         <v>93</v>
       </c>
@@ -41612,7 +41612,7 @@
       </c>
       <c r="F82" s="12"/>
     </row>
-    <row r="83" spans="1:6" ht="14.5" customHeight="1">
+    <row r="83" spans="1:6" ht="14.45" customHeight="1">
       <c r="A83" s="1">
         <v>94</v>
       </c>
@@ -42170,7 +42170,7 @@
       </c>
       <c r="F113" s="12"/>
     </row>
-    <row r="114" spans="1:6" ht="29">
+    <row r="114" spans="1:6" ht="30">
       <c r="A114" s="1">
         <v>125</v>
       </c>
@@ -42602,7 +42602,7 @@
       </c>
       <c r="F137" s="12"/>
     </row>
-    <row r="138" spans="1:6" ht="29">
+    <row r="138" spans="1:6" ht="30">
       <c r="A138" s="1">
         <v>149</v>
       </c>
@@ -42620,7 +42620,7 @@
       </c>
       <c r="F138" s="12"/>
     </row>
-    <row r="139" spans="1:6" ht="43.5">
+    <row r="139" spans="1:6" ht="45">
       <c r="A139" s="1">
         <v>150</v>
       </c>
@@ -42926,7 +42926,7 @@
       </c>
       <c r="F155" s="12"/>
     </row>
-    <row r="156" spans="1:6" ht="29">
+    <row r="156" spans="1:6" ht="30">
       <c r="A156" s="1">
         <v>167</v>
       </c>
@@ -43140,7 +43140,7 @@
       <c r="E169" s="1"/>
       <c r="F169" s="12"/>
     </row>
-    <row r="170" spans="1:6" ht="30">
+    <row r="170" spans="1:6" ht="30.75">
       <c r="A170" s="1"/>
       <c r="B170" s="1" t="s">
         <v>169</v>
@@ -43168,7 +43168,7 @@
       <c r="E171" s="1"/>
       <c r="F171" s="12"/>
     </row>
-    <row r="172" spans="1:6" ht="30">
+    <row r="172" spans="1:6" ht="45.75">
       <c r="A172" s="1"/>
       <c r="B172" s="1" t="s">
         <v>25</v>
@@ -43182,7 +43182,7 @@
       <c r="E172" s="1"/>
       <c r="F172" s="12"/>
     </row>
-    <row r="173" spans="1:6" ht="44.5">
+    <row r="173" spans="1:6" ht="45.75">
       <c r="A173" s="1"/>
       <c r="B173" s="1" t="s">
         <v>68</v>
@@ -43224,7 +43224,7 @@
       <c r="E175" s="1"/>
       <c r="F175" s="12"/>
     </row>
-    <row r="176" spans="1:6" ht="30">
+    <row r="176" spans="1:6" ht="30.75">
       <c r="A176" s="1"/>
       <c r="B176" s="1" t="s">
         <v>1021</v>
@@ -43280,7 +43280,7 @@
       <c r="E179" s="1"/>
       <c r="F179" s="12"/>
     </row>
-    <row r="180" spans="1:6" ht="30">
+    <row r="180" spans="1:6" ht="30.75">
       <c r="A180" s="1"/>
       <c r="B180" s="1" t="s">
         <v>77</v>
@@ -43518,7 +43518,7 @@
       <c r="E196" s="1"/>
       <c r="F196" s="12"/>
     </row>
-    <row r="197" spans="1:6" ht="16.5">
+    <row r="197" spans="1:6" ht="33">
       <c r="A197" s="1"/>
       <c r="B197" s="1" t="s">
         <v>247</v>
@@ -43532,7 +43532,7 @@
       <c r="E197" s="1"/>
       <c r="F197" s="12"/>
     </row>
-    <row r="198" spans="1:6" ht="16.5">
+    <row r="198" spans="1:6" ht="33">
       <c r="A198" s="1"/>
       <c r="B198" s="1" t="s">
         <v>1056</v>
@@ -43546,7 +43546,7 @@
       <c r="E198" s="1"/>
       <c r="F198" s="12"/>
     </row>
-    <row r="199" spans="1:6" ht="16.5">
+    <row r="199" spans="1:6" ht="33">
       <c r="A199" s="1"/>
       <c r="B199" s="1" t="s">
         <v>153</v>
@@ -43602,7 +43602,7 @@
       <c r="E202" s="1"/>
       <c r="F202" s="12"/>
     </row>
-    <row r="203" spans="1:6" ht="16.5">
+    <row r="203" spans="1:6" ht="30.75">
       <c r="A203" s="1"/>
       <c r="B203" s="1" t="s">
         <v>23</v>
@@ -43700,7 +43700,7 @@
       <c r="E209" s="1"/>
       <c r="F209" s="12"/>
     </row>
-    <row r="210" spans="1:6" ht="44.5">
+    <row r="210" spans="1:6" ht="45.75">
       <c r="A210" s="1"/>
       <c r="B210" s="1" t="s">
         <v>247</v>
@@ -43714,7 +43714,7 @@
       <c r="E210" s="1"/>
       <c r="F210" s="12"/>
     </row>
-    <row r="211" spans="1:6" ht="44.5">
+    <row r="211" spans="1:6" ht="60.75">
       <c r="A211" s="1"/>
       <c r="B211" s="1" t="s">
         <v>1077</v>
@@ -43728,7 +43728,7 @@
       <c r="E211" s="1"/>
       <c r="F211" s="12"/>
     </row>
-    <row r="212" spans="1:6" ht="16.5">
+    <row r="212" spans="1:6" ht="33">
       <c r="A212" s="1"/>
       <c r="B212" s="1" t="s">
         <v>1080</v>
@@ -43742,7 +43742,7 @@
       <c r="E212" s="1"/>
       <c r="F212" s="12"/>
     </row>
-    <row r="213" spans="1:6" ht="16.5">
+    <row r="213" spans="1:6" ht="33">
       <c r="A213" s="1"/>
       <c r="B213" s="1" t="s">
         <v>1082</v>
@@ -43756,7 +43756,7 @@
       <c r="E213" s="1"/>
       <c r="F213" s="12"/>
     </row>
-    <row r="214" spans="1:6" ht="16.5">
+    <row r="214" spans="1:6" ht="33">
       <c r="A214" s="1"/>
       <c r="B214" s="1" t="s">
         <v>1083</v>
@@ -43770,7 +43770,7 @@
       <c r="E214" s="1"/>
       <c r="F214" s="12"/>
     </row>
-    <row r="215" spans="1:6" ht="16.5">
+    <row r="215" spans="1:6" ht="33">
       <c r="A215" s="1"/>
       <c r="B215" s="1" t="s">
         <v>1084</v>
@@ -43784,7 +43784,7 @@
       <c r="E215" s="1"/>
       <c r="F215" s="12"/>
     </row>
-    <row r="216" spans="1:6" ht="16.5">
+    <row r="216" spans="1:6" ht="33">
       <c r="A216" s="1"/>
       <c r="B216" s="1" t="s">
         <v>1085</v>
@@ -43798,7 +43798,7 @@
       <c r="E216" s="1"/>
       <c r="F216" s="12"/>
     </row>
-    <row r="217" spans="1:6" ht="16.5">
+    <row r="217" spans="1:6" ht="33">
       <c r="A217" s="1"/>
       <c r="B217" s="1" t="s">
         <v>111</v>
@@ -43812,7 +43812,7 @@
       <c r="E217" s="1"/>
       <c r="F217" s="12"/>
     </row>
-    <row r="218" spans="1:6" ht="16.5">
+    <row r="218" spans="1:6" ht="33">
       <c r="A218" s="1"/>
       <c r="B218" s="1" t="s">
         <v>1087</v>
@@ -43826,7 +43826,7 @@
       <c r="E218" s="1"/>
       <c r="F218" s="12"/>
     </row>
-    <row r="219" spans="1:6" ht="16.5">
+    <row r="219" spans="1:6" ht="33">
       <c r="A219" s="1"/>
       <c r="B219" s="1" t="s">
         <v>1088</v>
@@ -43840,7 +43840,7 @@
       <c r="E219" s="1"/>
       <c r="F219" s="12"/>
     </row>
-    <row r="220" spans="1:6" ht="16.5">
+    <row r="220" spans="1:6" ht="33">
       <c r="A220" s="1"/>
       <c r="B220" s="1" t="s">
         <v>1090</v>
@@ -43854,7 +43854,7 @@
       <c r="E220" s="1"/>
       <c r="F220" s="12"/>
     </row>
-    <row r="221" spans="1:6" ht="16.5">
+    <row r="221" spans="1:6" ht="33">
       <c r="A221" s="1"/>
       <c r="B221" s="1" t="s">
         <v>1092</v>
@@ -43868,7 +43868,7 @@
       <c r="E221" s="1"/>
       <c r="F221" s="12"/>
     </row>
-    <row r="222" spans="1:6" ht="16.5">
+    <row r="222" spans="1:6" ht="33">
       <c r="A222" s="1"/>
       <c r="B222" s="1" t="s">
         <v>246</v>
@@ -43882,7 +43882,7 @@
       <c r="E222" s="1"/>
       <c r="F222" s="12"/>
     </row>
-    <row r="223" spans="1:6" ht="16.5">
+    <row r="223" spans="1:6" ht="33">
       <c r="A223" s="1"/>
       <c r="B223" s="1" t="s">
         <v>1094</v>
@@ -43896,7 +43896,7 @@
       <c r="E223" s="1"/>
       <c r="F223" s="12"/>
     </row>
-    <row r="224" spans="1:6" ht="16.5">
+    <row r="224" spans="1:6" ht="33">
       <c r="A224" s="1"/>
       <c r="B224" s="1" t="s">
         <v>1096</v>
@@ -43910,7 +43910,7 @@
       <c r="E224" s="1"/>
       <c r="F224" s="12"/>
     </row>
-    <row r="225" spans="1:6" ht="16.5">
+    <row r="225" spans="1:6" ht="33">
       <c r="A225" s="1"/>
       <c r="B225" s="1" t="s">
         <v>1098</v>
@@ -43924,7 +43924,7 @@
       <c r="E225" s="1"/>
       <c r="F225" s="12"/>
     </row>
-    <row r="226" spans="1:6" ht="16.5">
+    <row r="226" spans="1:6" ht="33">
       <c r="A226" s="1"/>
       <c r="B226" s="1" t="s">
         <v>1046</v>
@@ -43938,7 +43938,7 @@
       <c r="E226" s="1"/>
       <c r="F226" s="12"/>
     </row>
-    <row r="227" spans="1:6" ht="16.5">
+    <row r="227" spans="1:6" ht="33">
       <c r="A227" s="1"/>
       <c r="B227" s="1" t="s">
         <v>115</v>
@@ -43952,7 +43952,7 @@
       <c r="E227" s="1"/>
       <c r="F227" s="12"/>
     </row>
-    <row r="228" spans="1:6" ht="16.5">
+    <row r="228" spans="1:6" ht="33">
       <c r="A228" s="1"/>
       <c r="B228" s="1" t="s">
         <v>1099</v>
@@ -43966,7 +43966,7 @@
       <c r="E228" s="1"/>
       <c r="F228" s="12"/>
     </row>
-    <row r="229" spans="1:6" ht="30">
+    <row r="229" spans="1:6" ht="33">
       <c r="A229" s="1"/>
       <c r="B229" s="1" t="s">
         <v>1101</v>
@@ -43980,7 +43980,7 @@
       <c r="E229" s="1"/>
       <c r="F229" s="12"/>
     </row>
-    <row r="230" spans="1:6" ht="16.5">
+    <row r="230" spans="1:6" ht="33">
       <c r="A230" s="1"/>
       <c r="B230" s="1" t="s">
         <v>1103</v>
@@ -43994,7 +43994,7 @@
       <c r="E230" s="1"/>
       <c r="F230" s="12"/>
     </row>
-    <row r="231" spans="1:6" ht="16.5">
+    <row r="231" spans="1:6" ht="33">
       <c r="A231" s="1"/>
       <c r="B231" s="1" t="s">
         <v>153</v>
@@ -44008,7 +44008,7 @@
       <c r="E231" s="1"/>
       <c r="F231" s="12"/>
     </row>
-    <row r="232" spans="1:6" ht="16.5">
+    <row r="232" spans="1:6" ht="33">
       <c r="A232" s="1"/>
       <c r="B232" s="1" t="s">
         <v>1105</v>
@@ -44022,7 +44022,7 @@
       <c r="E232" s="1"/>
       <c r="F232" s="12"/>
     </row>
-    <row r="233" spans="1:6" ht="16.5">
+    <row r="233" spans="1:6" ht="33">
       <c r="A233" s="1"/>
       <c r="B233" s="1" t="s">
         <v>1107</v>
@@ -44036,7 +44036,7 @@
       <c r="E233" s="1"/>
       <c r="F233" s="12"/>
     </row>
-    <row r="234" spans="1:6" ht="16.5">
+    <row r="234" spans="1:6" ht="33">
       <c r="A234" s="1"/>
       <c r="B234" s="1" t="s">
         <v>1056</v>
@@ -44050,7 +44050,7 @@
       <c r="E234" s="1"/>
       <c r="F234" s="12"/>
     </row>
-    <row r="235" spans="1:6" ht="16.5">
+    <row r="235" spans="1:6" ht="33">
       <c r="A235" s="1"/>
       <c r="B235" s="1" t="s">
         <v>1052</v>
@@ -44064,7 +44064,7 @@
       <c r="E235" s="1"/>
       <c r="F235" s="12"/>
     </row>
-    <row r="236" spans="1:6" ht="16.5">
+    <row r="236" spans="1:6" ht="33">
       <c r="A236" s="1"/>
       <c r="B236" s="1" t="s">
         <v>247</v>
@@ -44078,7 +44078,7 @@
       <c r="E236" s="1"/>
       <c r="F236" s="12"/>
     </row>
-    <row r="237" spans="1:6" ht="16.5">
+    <row r="237" spans="1:6" ht="33">
       <c r="A237" s="1"/>
       <c r="B237" s="1" t="s">
         <v>1110</v>
@@ -44092,7 +44092,7 @@
       <c r="E237" s="1"/>
       <c r="F237" s="12"/>
     </row>
-    <row r="238" spans="1:6" ht="16.5">
+    <row r="238" spans="1:6" ht="33">
       <c r="A238" s="1"/>
       <c r="B238" s="1" t="s">
         <v>1112</v>
@@ -44106,7 +44106,7 @@
       <c r="E238" s="1"/>
       <c r="F238" s="12"/>
     </row>
-    <row r="239" spans="1:6" ht="16.5">
+    <row r="239" spans="1:6" ht="33">
       <c r="A239" s="1"/>
       <c r="B239" s="1" t="s">
         <v>1113</v>
@@ -44120,7 +44120,7 @@
       <c r="E239" s="1"/>
       <c r="F239" s="12"/>
     </row>
-    <row r="240" spans="1:6" ht="30">
+    <row r="240" spans="1:6" ht="33">
       <c r="A240" s="1"/>
       <c r="B240" s="1" t="s">
         <v>124</v>
@@ -44134,7 +44134,7 @@
       <c r="E240" s="1"/>
       <c r="F240" s="12"/>
     </row>
-    <row r="241" spans="1:6" ht="16.5">
+    <row r="241" spans="1:6" ht="33">
       <c r="A241" s="1"/>
       <c r="B241" s="1" t="s">
         <v>47</v>
@@ -44148,7 +44148,7 @@
       <c r="E241" s="1"/>
       <c r="F241" s="12"/>
     </row>
-    <row r="242" spans="1:6" ht="16.5">
+    <row r="242" spans="1:6" ht="33">
       <c r="A242" s="1"/>
       <c r="B242" s="1" t="s">
         <v>242</v>
@@ -44162,7 +44162,7 @@
       <c r="E242" s="1"/>
       <c r="F242" s="12"/>
     </row>
-    <row r="243" spans="1:6" ht="16.5">
+    <row r="243" spans="1:6" ht="33">
       <c r="A243" s="1"/>
       <c r="B243" s="1" t="s">
         <v>1115</v>
@@ -44176,7 +44176,7 @@
       <c r="E243" s="1"/>
       <c r="F243" s="12"/>
     </row>
-    <row r="244" spans="1:6" ht="30">
+    <row r="244" spans="1:6" ht="33">
       <c r="A244" s="1"/>
       <c r="B244" s="1" t="s">
         <v>1117</v>
@@ -44190,7 +44190,7 @@
       <c r="E244" s="1"/>
       <c r="F244" s="12"/>
     </row>
-    <row r="245" spans="1:6" ht="16.5">
+    <row r="245" spans="1:6" ht="33">
       <c r="A245" s="1"/>
       <c r="B245" s="1" t="s">
         <v>34</v>
@@ -44204,7 +44204,7 @@
       <c r="E245" s="1"/>
       <c r="F245" s="12"/>
     </row>
-    <row r="246" spans="1:6" ht="16.5">
+    <row r="246" spans="1:6" ht="33">
       <c r="A246" s="1"/>
       <c r="B246" s="1" t="s">
         <v>1120</v>
@@ -44218,7 +44218,7 @@
       <c r="E246" s="1"/>
       <c r="F246" s="12"/>
     </row>
-    <row r="247" spans="1:6" ht="16.5">
+    <row r="247" spans="1:6" ht="33">
       <c r="A247" s="1"/>
       <c r="B247" s="1" t="s">
         <v>1122</v>
@@ -44232,7 +44232,7 @@
       <c r="E247" s="1"/>
       <c r="F247" s="12"/>
     </row>
-    <row r="248" spans="1:6" ht="16.5">
+    <row r="248" spans="1:6" ht="33">
       <c r="A248" s="1"/>
       <c r="B248" s="1" t="s">
         <v>248</v>
@@ -44246,7 +44246,7 @@
       <c r="E248" s="1"/>
       <c r="F248" s="12"/>
     </row>
-    <row r="249" spans="1:6" ht="16.5">
+    <row r="249" spans="1:6" ht="33">
       <c r="A249" s="1"/>
       <c r="B249" s="1" t="s">
         <v>142</v>
@@ -44260,7 +44260,7 @@
       <c r="E249" s="1"/>
       <c r="F249" s="12"/>
     </row>
-    <row r="250" spans="1:6" ht="16.5">
+    <row r="250" spans="1:6" ht="33">
       <c r="A250" s="1"/>
       <c r="B250" s="1" t="s">
         <v>1125</v>
@@ -44274,7 +44274,7 @@
       <c r="E250" s="1"/>
       <c r="F250" s="12"/>
     </row>
-    <row r="251" spans="1:6" ht="16.5">
+    <row r="251" spans="1:6" ht="33">
       <c r="A251" s="1"/>
       <c r="B251" s="1" t="s">
         <v>136</v>
@@ -44288,7 +44288,7 @@
       <c r="E251" s="1"/>
       <c r="F251" s="12"/>
     </row>
-    <row r="252" spans="1:6" ht="16.5">
+    <row r="252" spans="1:6" ht="33">
       <c r="A252" s="1"/>
       <c r="B252" s="1" t="s">
         <v>1128</v>
@@ -44302,7 +44302,7 @@
       <c r="E252" s="1"/>
       <c r="F252" s="12"/>
     </row>
-    <row r="253" spans="1:6" ht="16.5">
+    <row r="253" spans="1:6" ht="33">
       <c r="A253" s="1"/>
       <c r="B253" s="1" t="s">
         <v>23</v>
@@ -44316,7 +44316,7 @@
       <c r="E253" s="1"/>
       <c r="F253" s="12"/>
     </row>
-    <row r="254" spans="1:6" ht="16.5">
+    <row r="254" spans="1:6" ht="33">
       <c r="A254" s="1"/>
       <c r="B254" s="1" t="s">
         <v>1131</v>
@@ -44330,7 +44330,7 @@
       <c r="E254" s="1"/>
       <c r="F254" s="12"/>
     </row>
-    <row r="255" spans="1:6" ht="16.5">
+    <row r="255" spans="1:6" ht="33">
       <c r="A255" s="1"/>
       <c r="B255" s="1" t="s">
         <v>1133</v>
@@ -44484,7 +44484,7 @@
       <c r="E265" s="1"/>
       <c r="F265" s="12"/>
     </row>
-    <row r="266" spans="1:6" ht="29">
+    <row r="266" spans="1:6" ht="30">
       <c r="A266" s="1"/>
       <c r="B266" s="1" t="s">
         <v>1125</v>
@@ -44582,7 +44582,7 @@
       <c r="E272" s="1"/>
       <c r="F272" s="12"/>
     </row>
-    <row r="273" spans="1:6" ht="44.5">
+    <row r="273" spans="1:6" ht="45.75">
       <c r="A273" s="1"/>
       <c r="B273" s="1" t="s">
         <v>100</v>
@@ -44652,7 +44652,7 @@
       <c r="E277" s="1"/>
       <c r="F277" s="12"/>
     </row>
-    <row r="278" spans="1:6" ht="30">
+    <row r="278" spans="1:6" ht="30.75">
       <c r="A278" s="1"/>
       <c r="B278" s="1" t="s">
         <v>1173</v>
@@ -44666,7 +44666,7 @@
       <c r="E278" s="1"/>
       <c r="F278" s="12"/>
     </row>
-    <row r="279" spans="1:6" ht="16.5">
+    <row r="279" spans="1:6" ht="30.75">
       <c r="A279" s="1"/>
       <c r="B279" s="1" t="s">
         <v>23</v>
@@ -44680,7 +44680,7 @@
       <c r="E279" s="1"/>
       <c r="F279" s="12"/>
     </row>
-    <row r="280" spans="1:6" ht="30">
+    <row r="280" spans="1:6" ht="30.75">
       <c r="A280" s="1"/>
       <c r="B280" s="1" t="s">
         <v>1176</v>
@@ -44694,7 +44694,7 @@
       <c r="E280" s="1"/>
       <c r="F280" s="12"/>
     </row>
-    <row r="281" spans="1:6" ht="30">
+    <row r="281" spans="1:6" ht="45.75">
       <c r="A281" s="1"/>
       <c r="B281" s="1" t="s">
         <v>1087</v>
@@ -44708,7 +44708,7 @@
       <c r="E281" s="1"/>
       <c r="F281" s="12"/>
     </row>
-    <row r="282" spans="1:6" ht="30">
+    <row r="282" spans="1:6" ht="30.75">
       <c r="A282" s="1"/>
       <c r="B282" s="1" t="s">
         <v>1179</v>
@@ -44750,7 +44750,7 @@
       <c r="E284" s="1"/>
       <c r="F284" s="12"/>
     </row>
-    <row r="285" spans="1:6" ht="88">
+    <row r="285" spans="1:6" ht="90.75">
       <c r="A285" s="1"/>
       <c r="B285" s="1" t="s">
         <v>1183</v>
@@ -44876,7 +44876,7 @@
       <c r="E293" s="1"/>
       <c r="F293" s="12"/>
     </row>
-    <row r="294" spans="1:6" ht="44.5">
+    <row r="294" spans="1:6" ht="45.75">
       <c r="A294" s="1"/>
       <c r="B294" s="1" t="s">
         <v>18</v>
@@ -44960,7 +44960,7 @@
       <c r="E299" s="1"/>
       <c r="F299" s="12"/>
     </row>
-    <row r="300" spans="1:6" ht="30">
+    <row r="300" spans="1:6" ht="30.75">
       <c r="A300" s="1"/>
       <c r="B300" s="1" t="s">
         <v>1205</v>
@@ -44988,7 +44988,7 @@
       <c r="E301" s="1"/>
       <c r="F301" s="12"/>
     </row>
-    <row r="302" spans="1:6" ht="16.5">
+    <row r="302" spans="1:6" ht="30.75">
       <c r="A302" s="1"/>
       <c r="B302" s="1" t="s">
         <v>38</v>
@@ -45044,7 +45044,7 @@
       <c r="E305" s="1"/>
       <c r="F305" s="12"/>
     </row>
-    <row r="306" spans="1:6" ht="33">
+    <row r="306" spans="1:6" ht="45.75">
       <c r="A306" s="1"/>
       <c r="B306" s="1" t="s">
         <v>73</v>
@@ -45058,7 +45058,7 @@
       <c r="E306" s="1"/>
       <c r="F306" s="12"/>
     </row>
-    <row r="307" spans="1:6" ht="44.5">
+    <row r="307" spans="1:6" ht="45.75">
       <c r="A307" s="1"/>
       <c r="B307" s="1" t="s">
         <v>1217</v>
@@ -45156,7 +45156,7 @@
       <c r="E313" s="1"/>
       <c r="F313" s="12"/>
     </row>
-    <row r="314" spans="1:6" ht="72.5">
+    <row r="314" spans="1:6" ht="90">
       <c r="A314" s="1"/>
       <c r="B314" s="1" t="s">
         <v>1229</v>
@@ -45240,7 +45240,7 @@
       <c r="E319" s="1"/>
       <c r="F319" s="12"/>
     </row>
-    <row r="320" spans="1:6" ht="29">
+    <row r="320" spans="1:6" ht="30">
       <c r="A320" s="1"/>
       <c r="B320" s="1" t="s">
         <v>1190</v>
@@ -45338,7 +45338,7 @@
       <c r="E326" s="1"/>
       <c r="F326" s="12"/>
     </row>
-    <row r="327" spans="1:6" ht="30">
+    <row r="327" spans="1:6" ht="30.75">
       <c r="A327" s="1"/>
       <c r="B327" s="1" t="s">
         <v>1252</v>
@@ -45366,7 +45366,7 @@
       <c r="E328" s="1"/>
       <c r="F328" s="12"/>
     </row>
-    <row r="329" spans="1:6" ht="116">
+    <row r="329" spans="1:6" ht="135">
       <c r="A329" s="1"/>
       <c r="B329" s="1" t="s">
         <v>1255</v>
@@ -45394,7 +45394,7 @@
       <c r="E330" s="1"/>
       <c r="F330" s="12"/>
     </row>
-    <row r="331" spans="1:6" ht="29">
+    <row r="331" spans="1:6" ht="30">
       <c r="A331" s="1"/>
       <c r="B331" s="1" t="s">
         <v>30</v>
@@ -45408,7 +45408,7 @@
       <c r="E331" s="1"/>
       <c r="F331" s="12"/>
     </row>
-    <row r="332" spans="1:6" ht="29">
+    <row r="332" spans="1:6" ht="30">
       <c r="A332" s="1"/>
       <c r="B332" s="1" t="s">
         <v>1013</v>
@@ -45422,7 +45422,7 @@
       <c r="E332" s="1"/>
       <c r="F332" s="12"/>
     </row>
-    <row r="333" spans="1:6" ht="29">
+    <row r="333" spans="1:6" ht="30">
       <c r="A333" s="1"/>
       <c r="B333" s="1" t="s">
         <v>1176</v>
@@ -45604,7 +45604,7 @@
       <c r="E345" s="1"/>
       <c r="F345" s="12"/>
     </row>
-    <row r="636" spans="1:5" ht="58">
+    <row r="636" spans="1:5" ht="60">
       <c r="A636">
         <v>186</v>
       </c>
@@ -45634,7 +45634,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="638" spans="1:5" ht="29">
+    <row r="638" spans="1:5" ht="30">
       <c r="A638">
         <v>188</v>
       </c>
@@ -45679,7 +45679,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="29">
+    <row r="641" spans="1:5" ht="30">
       <c r="A641">
         <v>191</v>
       </c>
@@ -45694,7 +45694,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="642" spans="1:5" ht="29">
+    <row r="642" spans="1:5" ht="30">
       <c r="A642">
         <v>192</v>
       </c>
@@ -45709,7 +45709,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="643" spans="1:5" ht="43.5">
+    <row r="643" spans="1:5" ht="45">
       <c r="A643">
         <v>193</v>
       </c>
@@ -45724,7 +45724,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="644" spans="1:5" ht="43.5">
+    <row r="644" spans="1:5" ht="45">
       <c r="A644">
         <v>194</v>
       </c>
@@ -45828,7 +45828,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="651" spans="1:5" ht="14.5" customHeight="1">
+    <row r="651" spans="1:5" ht="14.45" customHeight="1">
       <c r="A651">
         <v>201</v>
       </c>
@@ -45842,7 +45842,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="652" spans="1:5" ht="14.5" customHeight="1">
+    <row r="652" spans="1:5" ht="14.45" customHeight="1">
       <c r="A652">
         <v>202</v>
       </c>
@@ -45870,7 +45870,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="654" spans="1:5" ht="14.5" customHeight="1">
+    <row r="654" spans="1:5" ht="14.45" customHeight="1">
       <c r="A654">
         <v>204</v>
       </c>
@@ -45884,7 +45884,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="655" spans="1:5" ht="14.5" customHeight="1">
+    <row r="655" spans="1:5" ht="14.45" customHeight="1">
       <c r="A655">
         <v>205</v>
       </c>
@@ -45968,7 +45968,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="661" spans="1:5" ht="188.5">
+    <row r="661" spans="1:5" ht="210">
       <c r="A661">
         <v>211</v>
       </c>
@@ -45982,7 +45982,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="662" spans="1:5" ht="203">
+    <row r="662" spans="1:5" ht="225">
       <c r="A662">
         <v>212</v>
       </c>
@@ -45996,7 +45996,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="663" spans="1:5" ht="203">
+    <row r="663" spans="1:5" ht="210">
       <c r="A663">
         <v>213</v>
       </c>
@@ -46024,7 +46024,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="665" spans="1:5" ht="174">
+    <row r="665" spans="1:5" ht="180">
       <c r="A665">
         <v>215</v>
       </c>
@@ -46038,7 +46038,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="666" spans="1:5" ht="159.5">
+    <row r="666" spans="1:5" ht="165">
       <c r="A666">
         <v>216</v>
       </c>
@@ -46133,7 +46133,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="673" spans="1:5" ht="188.5">
+    <row r="673" spans="1:5" ht="195">
       <c r="A673">
         <v>223</v>
       </c>
@@ -46147,7 +46147,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="674" spans="1:5" ht="29">
+    <row r="674" spans="1:5" ht="30">
       <c r="A674">
         <v>224</v>
       </c>
@@ -46189,7 +46189,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="677" spans="1:5" ht="43.5">
+    <row r="677" spans="1:5" ht="45">
       <c r="A677">
         <v>227</v>
       </c>
@@ -46203,7 +46203,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="678" spans="1:5" ht="159.5">
+    <row r="678" spans="1:5" ht="165">
       <c r="A678">
         <v>228</v>
       </c>
@@ -46231,7 +46231,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="680" spans="1:5" ht="29">
+    <row r="680" spans="1:5" ht="30">
       <c r="A680">
         <v>230</v>
       </c>
@@ -46273,7 +46273,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="683" spans="1:5" ht="159.5">
+    <row r="683" spans="1:5" ht="180">
       <c r="A683">
         <v>233</v>
       </c>
@@ -46287,7 +46287,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="684" spans="1:5" ht="29">
+    <row r="684" spans="1:5" ht="30">
       <c r="A684">
         <v>234</v>
       </c>
@@ -46329,7 +46329,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="687" spans="1:5" ht="43.5">
+    <row r="687" spans="1:5" ht="45">
       <c r="A687">
         <v>237</v>
       </c>
@@ -46343,7 +46343,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="688" spans="1:5" ht="159.5">
+    <row r="688" spans="1:5" ht="180">
       <c r="A688">
         <v>238</v>
       </c>
@@ -46357,7 +46357,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="689" spans="1:5" ht="174">
+    <row r="689" spans="1:5" ht="195">
       <c r="A689">
         <v>239</v>
       </c>
@@ -46385,7 +46385,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="691" spans="1:5" ht="159.5">
+    <row r="691" spans="1:5" ht="180">
       <c r="A691">
         <v>241</v>
       </c>
@@ -46427,7 +46427,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="694" spans="1:5" ht="43.5">
+    <row r="694" spans="1:5" ht="45">
       <c r="A694">
         <v>244</v>
       </c>
@@ -46455,7 +46455,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="696" spans="1:5" ht="29">
+    <row r="696" spans="1:5" ht="45">
       <c r="A696">
         <v>246</v>
       </c>
@@ -46497,7 +46497,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="699" spans="1:5" ht="29">
+    <row r="699" spans="1:5" ht="30">
       <c r="A699">
         <v>249</v>
       </c>
@@ -46525,7 +46525,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="701" spans="1:5" ht="29">
+    <row r="701" spans="1:5" ht="30">
       <c r="A701">
         <v>251</v>
       </c>
@@ -46539,7 +46539,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="702" spans="1:5" ht="130.5">
+    <row r="702" spans="1:5" ht="165">
       <c r="A702">
         <v>252</v>
       </c>
@@ -46595,7 +46595,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="706" spans="1:5" ht="43.5">
+    <row r="706" spans="1:5" ht="60">
       <c r="A706">
         <v>256</v>
       </c>
@@ -46637,7 +46637,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="709" spans="1:5" ht="58">
+    <row r="709" spans="1:5" ht="75">
       <c r="A709">
         <v>259</v>
       </c>
@@ -46651,7 +46651,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="710" spans="1:5" ht="29">
+    <row r="710" spans="1:5" ht="30">
       <c r="A710">
         <v>260</v>
       </c>
@@ -46749,7 +46749,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="717" spans="1:5" ht="58">
+    <row r="717" spans="1:5" ht="75">
       <c r="A717">
         <v>267</v>
       </c>
@@ -46777,7 +46777,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="719" spans="1:5" ht="43.5">
+    <row r="719" spans="1:5" ht="45">
       <c r="A719">
         <v>269</v>
       </c>
@@ -46819,7 +46819,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="722" spans="1:5" ht="29">
+    <row r="722" spans="1:5" ht="30">
       <c r="A722">
         <v>272</v>
       </c>
@@ -46903,7 +46903,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="728" spans="1:5" ht="29">
+    <row r="728" spans="1:5" ht="30">
       <c r="A728">
         <v>278</v>
       </c>
@@ -46917,7 +46917,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="729" spans="1:5" ht="29">
+    <row r="729" spans="1:5" ht="30">
       <c r="A729">
         <v>279</v>
       </c>
@@ -46931,7 +46931,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="730" spans="1:5" ht="29">
+    <row r="730" spans="1:5" ht="30">
       <c r="A730">
         <v>280</v>
       </c>
@@ -46959,7 +46959,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="732" spans="1:5" ht="29">
+    <row r="732" spans="1:5" ht="30">
       <c r="A732">
         <v>282</v>
       </c>
@@ -47001,7 +47001,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="735" spans="1:5" ht="29">
+    <row r="735" spans="1:5" ht="30">
       <c r="A735">
         <v>285</v>
       </c>
@@ -47015,7 +47015,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="736" spans="1:5" ht="72.5">
+    <row r="736" spans="1:5" ht="75">
       <c r="A736">
         <v>286</v>
       </c>
@@ -47099,7 +47099,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="742" spans="1:5" ht="29">
+    <row r="742" spans="1:5" ht="30">
       <c r="A742">
         <v>292</v>
       </c>
@@ -47127,7 +47127,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="744" spans="1:5" ht="29">
+    <row r="744" spans="1:5" ht="45">
       <c r="A744">
         <v>294</v>
       </c>
@@ -47155,7 +47155,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="746" spans="1:5" ht="29">
+    <row r="746" spans="1:5" ht="30">
       <c r="A746">
         <v>296</v>
       </c>
@@ -47183,7 +47183,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="748" spans="1:5" ht="29">
+    <row r="748" spans="1:5" ht="30">
       <c r="A748">
         <v>298</v>
       </c>
@@ -47225,7 +47225,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="751" spans="1:5" ht="43.5">
+    <row r="751" spans="1:5" ht="45">
       <c r="A751">
         <v>301</v>
       </c>
@@ -47253,7 +47253,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="753" spans="1:5" ht="29">
+    <row r="753" spans="1:5" ht="30">
       <c r="A753">
         <v>303</v>
       </c>
@@ -47281,7 +47281,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="755" spans="1:5" ht="29">
+    <row r="755" spans="1:5" ht="30">
       <c r="A755">
         <v>305</v>
       </c>
@@ -47309,7 +47309,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="757" spans="1:5" ht="29">
+    <row r="757" spans="1:5" ht="30">
       <c r="A757">
         <v>307</v>
       </c>
@@ -47337,7 +47337,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="759" spans="1:5" ht="29">
+    <row r="759" spans="1:5" ht="30">
       <c r="A759">
         <v>309</v>
       </c>
@@ -47365,7 +47365,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="761" spans="1:5" ht="43.5">
+    <row r="761" spans="1:5" ht="45">
       <c r="A761">
         <v>311</v>
       </c>
@@ -47407,7 +47407,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="764" spans="1:5" ht="29">
+    <row r="764" spans="1:5" ht="45">
       <c r="A764">
         <v>314</v>
       </c>
@@ -47421,7 +47421,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="765" spans="1:5" ht="43.5">
+    <row r="765" spans="1:5" ht="45">
       <c r="A765">
         <v>315</v>
       </c>
@@ -47477,7 +47477,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="769" spans="1:5">
+    <row r="769" spans="1:5" ht="30">
       <c r="A769">
         <v>319</v>
       </c>
@@ -47505,7 +47505,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="771" spans="1:5" ht="29">
+    <row r="771" spans="1:5" ht="30">
       <c r="A771">
         <v>321</v>
       </c>
@@ -47519,7 +47519,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="772" spans="1:5" ht="29">
+    <row r="772" spans="1:5" ht="30">
       <c r="A772">
         <v>322</v>
       </c>
@@ -47533,7 +47533,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="773" spans="1:5" ht="29">
+    <row r="773" spans="1:5" ht="30">
       <c r="A773">
         <v>323</v>
       </c>
@@ -47575,7 +47575,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="776" spans="1:5" ht="29">
+    <row r="776" spans="1:5" ht="30">
       <c r="A776">
         <v>326</v>
       </c>
@@ -47589,7 +47589,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="777" spans="1:5" ht="159.5">
+    <row r="777" spans="1:5" ht="165">
       <c r="A777">
         <v>327</v>
       </c>
@@ -47603,7 +47603,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="778" spans="1:5" ht="145">
+    <row r="778" spans="1:5" ht="165">
       <c r="A778">
         <v>328</v>
       </c>
@@ -47617,7 +47617,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="779" spans="1:5" ht="159.5">
+    <row r="779" spans="1:5" ht="165">
       <c r="A779">
         <v>329</v>
       </c>
@@ -47631,7 +47631,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="780" spans="1:5" ht="29">
+    <row r="780" spans="1:5" ht="30">
       <c r="A780">
         <v>330</v>
       </c>
@@ -47715,7 +47715,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="786" spans="1:5" ht="29">
+    <row r="786" spans="1:5" ht="30">
       <c r="A786">
         <v>336</v>
       </c>
@@ -47729,7 +47729,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="787" spans="1:5" ht="29">
+    <row r="787" spans="1:5" ht="30">
       <c r="A787">
         <v>337</v>
       </c>
@@ -47743,7 +47743,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="788" spans="1:5" ht="43.5">
+    <row r="788" spans="1:5" ht="60">
       <c r="A788">
         <v>338</v>
       </c>
@@ -47785,7 +47785,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="791" spans="1:5" ht="159.5">
+    <row r="791" spans="1:5" ht="165">
       <c r="A791">
         <v>341</v>
       </c>
@@ -47799,7 +47799,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="792" spans="1:5" ht="174">
+    <row r="792" spans="1:5" ht="180">
       <c r="A792">
         <v>342</v>
       </c>
@@ -47827,7 +47827,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="794" spans="1:5" ht="29">
+    <row r="794" spans="1:5" ht="30">
       <c r="A794">
         <v>344</v>
       </c>
@@ -47950,7 +47950,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="803" spans="1:5" ht="43.5">
+    <row r="803" spans="1:5" ht="45">
       <c r="A803">
         <v>353</v>
       </c>
@@ -48006,7 +48006,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="807" spans="1:5" ht="29">
+    <row r="807" spans="1:5" ht="30">
       <c r="A807">
         <v>357</v>
       </c>
@@ -48048,7 +48048,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="810" spans="1:5" ht="29">
+    <row r="810" spans="1:5" ht="30">
       <c r="A810">
         <v>360</v>
       </c>
@@ -48076,7 +48076,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="812" spans="1:5">
+    <row r="812" spans="1:5" ht="30">
       <c r="A812">
         <v>362</v>
       </c>
@@ -48118,7 +48118,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="815" spans="1:5" ht="29">
+    <row r="815" spans="1:5" ht="30">
       <c r="A815">
         <v>365</v>
       </c>
@@ -48202,7 +48202,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="821" spans="1:5" ht="43.5">
+    <row r="821" spans="1:5" ht="45">
       <c r="A821">
         <v>371</v>
       </c>
@@ -48216,7 +48216,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="822" spans="1:5" ht="43.5">
+    <row r="822" spans="1:5" ht="45">
       <c r="A822">
         <v>372</v>
       </c>
@@ -48454,7 +48454,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="839" spans="1:5" ht="29">
+    <row r="839" spans="1:5" ht="30">
       <c r="A839">
         <v>389</v>
       </c>
@@ -48468,7 +48468,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="840" spans="1:5">
+    <row r="840" spans="1:5" ht="30">
       <c r="A840">
         <v>390</v>
       </c>
@@ -48482,7 +48482,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="841" spans="1:5" ht="29">
+    <row r="841" spans="1:5" ht="30">
       <c r="A841">
         <v>391</v>
       </c>
@@ -48538,7 +48538,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="845" spans="1:5" ht="29">
+    <row r="845" spans="1:5" ht="30">
       <c r="A845">
         <v>395</v>
       </c>
@@ -48552,7 +48552,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="846" spans="1:5">
+    <row r="846" spans="1:5" ht="30">
       <c r="A846">
         <v>396</v>
       </c>
@@ -48580,7 +48580,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="848" spans="1:5" ht="29">
+    <row r="848" spans="1:5" ht="30">
       <c r="A848">
         <v>398</v>
       </c>
@@ -48594,7 +48594,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="849" spans="1:5" ht="29">
+    <row r="849" spans="1:5" ht="30">
       <c r="A849">
         <v>399</v>
       </c>
@@ -48650,7 +48650,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="853" spans="1:5">
+    <row r="853" spans="1:5" ht="30">
       <c r="A853">
         <v>403</v>
       </c>
@@ -48678,7 +48678,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="855" spans="1:5">
+    <row r="855" spans="1:5" ht="30">
       <c r="A855">
         <v>405</v>
       </c>
@@ -48692,7 +48692,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="856" spans="1:5" ht="29">
+    <row r="856" spans="1:5" ht="30">
       <c r="A856">
         <v>406</v>
       </c>
@@ -48832,7 +48832,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="866" spans="1:5" ht="145">
+    <row r="866" spans="1:5" ht="150">
       <c r="A866">
         <v>416</v>
       </c>
@@ -48874,7 +48874,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="869" spans="1:5" ht="58">
+    <row r="869" spans="1:5" ht="60">
       <c r="A869">
         <v>419</v>
       </c>
@@ -48944,7 +48944,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="874" spans="1:5" ht="29">
+    <row r="874" spans="1:5" ht="30">
       <c r="A874">
         <v>424</v>
       </c>
@@ -49014,7 +49014,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="879" spans="1:5" ht="29">
+    <row r="879" spans="1:5" ht="30">
       <c r="A879">
         <v>429</v>
       </c>
@@ -49028,7 +49028,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="880" spans="1:5" ht="29">
+    <row r="880" spans="1:5" ht="30">
       <c r="A880">
         <v>430</v>
       </c>
@@ -49126,7 +49126,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="887" spans="1:5" ht="29">
+    <row r="887" spans="1:5" ht="30">
       <c r="A887">
         <v>437</v>
       </c>
@@ -49319,7 +49319,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="901" spans="1:5" ht="29">
+    <row r="901" spans="1:5" ht="30">
       <c r="A901">
         <v>451</v>
       </c>
@@ -49333,7 +49333,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="902" spans="1:5" ht="174">
+    <row r="902" spans="1:5" ht="195">
       <c r="A902">
         <v>452</v>
       </c>
@@ -49347,7 +49347,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="903" spans="1:5" ht="145">
+    <row r="903" spans="1:5" ht="165">
       <c r="A903">
         <v>453</v>
       </c>
@@ -49361,7 +49361,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="904" spans="1:5">
+    <row r="904" spans="1:5" ht="30">
       <c r="A904">
         <v>454</v>
       </c>
@@ -49445,7 +49445,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="910" spans="1:5" ht="43.5">
+    <row r="910" spans="1:5" ht="45">
       <c r="A910">
         <v>460</v>
       </c>
@@ -49501,7 +49501,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="914" spans="1:5" ht="29">
+    <row r="914" spans="1:5" ht="30">
       <c r="A914">
         <v>464</v>
       </c>
@@ -49641,7 +49641,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="924" spans="1:5" ht="29">
+    <row r="924" spans="1:5" ht="30">
       <c r="A924">
         <v>474</v>
       </c>
@@ -49683,7 +49683,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="927" spans="1:5" ht="58">
+    <row r="927" spans="1:5" ht="60">
       <c r="A927">
         <v>477</v>
       </c>
@@ -49823,7 +49823,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="937" spans="1:5" ht="29">
+    <row r="937" spans="1:5" ht="30">
       <c r="A937">
         <v>487</v>
       </c>
@@ -49837,7 +49837,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="938" spans="1:5" ht="116">
+    <row r="938" spans="1:5" ht="120">
       <c r="A938">
         <v>488</v>
       </c>
@@ -49851,7 +49851,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="939" spans="1:5" ht="29">
+    <row r="939" spans="1:5" ht="30">
       <c r="A939">
         <v>489</v>
       </c>
@@ -49879,7 +49879,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="941" spans="1:5" ht="43.5">
+    <row r="941" spans="1:5" ht="45">
       <c r="A941">
         <v>491</v>
       </c>
@@ -49949,7 +49949,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="946" spans="1:5" ht="29">
+    <row r="946" spans="1:5" ht="30">
       <c r="A946">
         <v>496</v>
       </c>
@@ -49963,7 +49963,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="947" spans="1:5" ht="29">
+    <row r="947" spans="1:5" ht="30">
       <c r="A947">
         <v>497</v>
       </c>
@@ -49991,7 +49991,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="949" spans="1:5">
+    <row r="949" spans="1:5" ht="30">
       <c r="A949">
         <v>499</v>
       </c>
@@ -50005,7 +50005,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="950" spans="1:5" ht="29">
+    <row r="950" spans="1:5" ht="30">
       <c r="A950">
         <v>500</v>
       </c>
@@ -50019,7 +50019,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="951" spans="1:5" ht="29">
+    <row r="951" spans="1:5" ht="30">
       <c r="A951">
         <v>501</v>
       </c>
@@ -50033,7 +50033,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="952" spans="1:5" ht="29">
+    <row r="952" spans="1:5" ht="30">
       <c r="A952">
         <v>502</v>
       </c>
@@ -50047,7 +50047,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="953" spans="1:5" ht="43.5">
+    <row r="953" spans="1:5" ht="45">
       <c r="A953">
         <v>503</v>
       </c>
@@ -50061,7 +50061,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="954" spans="1:5" ht="29">
+    <row r="954" spans="1:5" ht="30">
       <c r="A954">
         <v>504</v>
       </c>
@@ -50089,7 +50089,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="956" spans="1:5" ht="43.5">
+    <row r="956" spans="1:5" ht="45">
       <c r="A956">
         <v>506</v>
       </c>
@@ -50128,7 +50128,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="959" spans="1:5" ht="159.5">
+    <row r="959" spans="1:5" ht="165">
       <c r="A959">
         <v>509</v>
       </c>
@@ -50142,7 +50142,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="960" spans="1:5" ht="159.5">
+    <row r="960" spans="1:5" ht="165">
       <c r="A960">
         <v>510</v>
       </c>
@@ -50170,7 +50170,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="962" spans="1:5" ht="43.5">
+    <row r="962" spans="1:5" ht="60">
       <c r="A962">
         <v>512</v>
       </c>
@@ -50184,7 +50184,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="963" spans="1:5" ht="159.5">
+    <row r="963" spans="1:5" ht="165">
       <c r="A963">
         <v>513</v>
       </c>
@@ -50212,7 +50212,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="965" spans="1:5" ht="58">
+    <row r="965" spans="1:5" ht="75">
       <c r="A965">
         <v>515</v>
       </c>
@@ -50226,7 +50226,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="966" spans="1:5">
+    <row r="966" spans="1:5" ht="30">
       <c r="A966">
         <v>516</v>
       </c>
@@ -50282,7 +50282,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="970" spans="1:5" ht="29">
+    <row r="970" spans="1:5" ht="30">
       <c r="A970">
         <v>520</v>
       </c>
@@ -50310,7 +50310,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="972" spans="1:5" ht="43.5">
+    <row r="972" spans="1:5" ht="45">
       <c r="A972">
         <v>522</v>
       </c>
@@ -50352,7 +50352,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="975" spans="1:5" ht="29">
+    <row r="975" spans="1:5" ht="30">
       <c r="A975">
         <v>525</v>
       </c>
@@ -50534,7 +50534,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="988" spans="1:5" ht="43.5">
+    <row r="988" spans="1:5" ht="45">
       <c r="A988">
         <v>538</v>
       </c>
@@ -50604,7 +50604,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="993" spans="1:5" ht="29">
+    <row r="993" spans="1:5" ht="30">
       <c r="A993">
         <v>543</v>
       </c>
@@ -50660,7 +50660,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="997" spans="1:5" ht="72.5">
+    <row r="997" spans="1:5" ht="75">
       <c r="A997">
         <v>547</v>
       </c>
@@ -50688,7 +50688,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="999" spans="1:5" ht="29">
+    <row r="999" spans="1:5" ht="30">
       <c r="A999">
         <v>549</v>
       </c>
@@ -50898,7 +50898,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1014" spans="1:5" ht="29">
+    <row r="1014" spans="1:5" ht="30">
       <c r="A1014">
         <v>564</v>
       </c>
@@ -50940,7 +50940,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1017" spans="1:5" ht="43.5">
+    <row r="1017" spans="1:5" ht="45">
       <c r="A1017">
         <v>567</v>
       </c>
@@ -50982,7 +50982,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1020" spans="1:5">
+    <row r="1020" spans="1:5" ht="30">
       <c r="A1020">
         <v>570</v>
       </c>
@@ -50996,7 +50996,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1021" spans="1:5" ht="58">
+    <row r="1021" spans="1:5" ht="60">
       <c r="A1021">
         <v>571</v>
       </c>
@@ -51010,7 +51010,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1022" spans="1:5" ht="43.5">
+    <row r="1022" spans="1:5" ht="45">
       <c r="A1022">
         <v>572</v>
       </c>
@@ -51024,7 +51024,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1023" spans="1:5" ht="58">
+    <row r="1023" spans="1:5" ht="60">
       <c r="A1023">
         <v>573</v>
       </c>
@@ -51038,7 +51038,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1024" spans="1:5" ht="29">
+    <row r="1024" spans="1:5" ht="30">
       <c r="A1024">
         <v>574</v>
       </c>
@@ -51276,7 +51276,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1041" spans="1:5" ht="43.5">
+    <row r="1041" spans="1:5" ht="45">
       <c r="A1041">
         <v>591</v>
       </c>
@@ -51290,7 +51290,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1042" spans="1:5" ht="29">
+    <row r="1042" spans="1:5" ht="30">
       <c r="A1042">
         <v>592</v>
       </c>
@@ -51304,7 +51304,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1043" spans="1:5" ht="29">
+    <row r="1043" spans="1:5" ht="30">
       <c r="A1043">
         <v>593</v>
       </c>
@@ -51318,7 +51318,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1044" spans="1:5" ht="58">
+    <row r="1044" spans="1:5" ht="60">
       <c r="A1044">
         <v>594</v>
       </c>
@@ -51346,7 +51346,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1046" spans="1:5" ht="43.5">
+    <row r="1046" spans="1:5" ht="45">
       <c r="A1046">
         <v>596</v>
       </c>
@@ -51430,7 +51430,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1052" spans="1:5" ht="29">
+    <row r="1052" spans="1:5" ht="30">
       <c r="A1052">
         <v>602</v>
       </c>
@@ -51556,7 +51556,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1061" spans="1:5" ht="116">
+    <row r="1061" spans="1:5" ht="120">
       <c r="A1061">
         <v>611</v>
       </c>
@@ -51584,7 +51584,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1063" spans="1:5" ht="29">
+    <row r="1063" spans="1:5" ht="30">
       <c r="A1063">
         <v>613</v>
       </c>
@@ -51612,7 +51612,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1065" spans="1:5" ht="43.5">
+    <row r="1065" spans="1:5" ht="45">
       <c r="A1065">
         <v>615</v>
       </c>
@@ -51626,7 +51626,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1066" spans="1:5">
+    <row r="1066" spans="1:5" ht="30">
       <c r="A1066">
         <v>616</v>
       </c>
@@ -51640,7 +51640,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1067" spans="1:5" ht="58">
+    <row r="1067" spans="1:5" ht="60">
       <c r="A1067">
         <v>617</v>
       </c>
@@ -51654,7 +51654,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1068" spans="1:5" ht="29">
+    <row r="1068" spans="1:5" ht="30">
       <c r="A1068">
         <v>618</v>
       </c>
@@ -51668,7 +51668,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1069" spans="1:5" ht="29">
+    <row r="1069" spans="1:5" ht="30">
       <c r="A1069">
         <v>619</v>
       </c>
@@ -51682,7 +51682,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1070" spans="1:5" ht="275.5">
+    <row r="1070" spans="1:5" ht="315">
       <c r="A1070">
         <v>620</v>
       </c>
@@ -51822,7 +51822,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1080" spans="1:5" ht="58">
+    <row r="1080" spans="1:5" ht="60">
       <c r="A1080">
         <v>630</v>
       </c>
@@ -51836,7 +51836,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1081" spans="1:5" ht="29">
+    <row r="1081" spans="1:5" ht="30">
       <c r="A1081">
         <v>631</v>
       </c>
@@ -51850,7 +51850,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1082" spans="1:5" ht="29">
+    <row r="1082" spans="1:5" ht="30">
       <c r="A1082">
         <v>632</v>
       </c>
@@ -51906,7 +51906,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1086" spans="1:5" ht="29">
+    <row r="1086" spans="1:5" ht="30">
       <c r="A1086">
         <v>636</v>
       </c>
@@ -51920,7 +51920,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1087" spans="1:5" ht="87">
+    <row r="1087" spans="1:5" ht="90">
       <c r="A1087">
         <v>637</v>
       </c>
@@ -51948,7 +51948,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1089" spans="1:5" ht="43.5">
+    <row r="1089" spans="1:5" ht="45">
       <c r="A1089">
         <v>639</v>
       </c>
@@ -51990,7 +51990,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1092" spans="1:5" ht="29">
+    <row r="1092" spans="1:5" ht="30">
       <c r="A1092">
         <v>642</v>
       </c>
@@ -52060,7 +52060,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1097" spans="1:5" ht="145">
+    <row r="1097" spans="1:5" ht="150">
       <c r="A1097">
         <v>647</v>
       </c>
@@ -52130,7 +52130,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1102" spans="1:5" ht="43.5">
+    <row r="1102" spans="1:5" ht="45">
       <c r="A1102">
         <v>652</v>
       </c>
@@ -52200,7 +52200,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1107" spans="1:5" ht="29">
+    <row r="1107" spans="1:5" ht="30">
       <c r="A1107">
         <v>657</v>
       </c>
@@ -52256,7 +52256,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1111" spans="1:5" ht="58">
+    <row r="1111" spans="1:5" ht="60">
       <c r="A1111">
         <v>661</v>
       </c>
@@ -52284,7 +52284,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1113" spans="1:5" ht="29">
+    <row r="1113" spans="1:5" ht="30">
       <c r="A1113">
         <v>663</v>
       </c>
@@ -52368,7 +52368,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="1119" spans="1:5" ht="58">
+    <row r="1119" spans="1:5" ht="60">
       <c r="A1119">
         <v>669</v>
       </c>
@@ -52422,7 +52422,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B807D2A0-D763-47A7-A989-A34C4F909D14}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" t="s">
